--- a/research/traditional_assets/database/data/south_africa/south_africa_environmental_waste_services.xlsx
+++ b/research/traditional_assets/database/data/south_africa/south_africa_environmental_waste_services.xlsx
@@ -1260,7 +1260,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1397,22 +1397,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1129343413283539</v>
+        <v>0.1126622686067674</v>
       </c>
       <c r="C2">
-        <v>17.56358524228995</v>
+        <v>17.4592750943584</v>
       </c>
       <c r="D2">
-        <v>17.51958524228995</v>
+        <v>17.5908750943584</v>
       </c>
       <c r="E2">
-        <v>-11.3</v>
+        <v>-11.1244</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.1756</v>
       </c>
       <c r="G2">
         <v>0.044</v>
@@ -1433,28 +1433,28 @@
         <v>5.074</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.008832680000000001</v>
       </c>
       <c r="N2">
-        <v>5.074</v>
+        <v>5.06516732</v>
       </c>
       <c r="O2">
-        <v>1.36998</v>
+        <v>1.3675951764</v>
       </c>
       <c r="P2">
-        <v>3.70402</v>
+        <v>3.6975721436</v>
       </c>
       <c r="Q2">
-        <v>4.59002</v>
+        <v>4.5835721436</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1129343413283539</v>
+        <v>0.113429372330068</v>
       </c>
       <c r="T2">
-        <v>0.8042521102410373</v>
+        <v>0.8101824540842288</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>574.4575825230846</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1479,22 +1479,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1126622686067674</v>
+        <v>0.1123901958851808</v>
       </c>
       <c r="C3">
-        <v>17.4592750943584</v>
+        <v>17.35554749536866</v>
       </c>
       <c r="D3">
-        <v>17.5908750943584</v>
+        <v>17.66274749536866</v>
       </c>
       <c r="E3">
-        <v>-11.1244</v>
+        <v>-10.9488</v>
       </c>
       <c r="F3">
-        <v>0.1756</v>
+        <v>0.3512000000000001</v>
       </c>
       <c r="G3">
         <v>0.044</v>
@@ -1515,28 +1515,28 @@
         <v>5.074</v>
       </c>
       <c r="M3">
-        <v>0.008832680000000001</v>
+        <v>0.01766536</v>
       </c>
       <c r="N3">
-        <v>5.06516732</v>
+        <v>5.05633464</v>
       </c>
       <c r="O3">
-        <v>1.3675951764</v>
+        <v>1.3652103528</v>
       </c>
       <c r="P3">
-        <v>3.6975721436</v>
+        <v>3.6911242872</v>
       </c>
       <c r="Q3">
-        <v>4.5835721436</v>
+        <v>4.5771242872</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.113429372330068</v>
+        <v>0.1139345060052865</v>
       </c>
       <c r="T3">
-        <v>0.8101824540842288</v>
+        <v>0.8162338253527915</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>574.4575825230846</v>
+        <v>287.2287912615424</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1123901958851808</v>
+        <v>0.1121181231635942</v>
       </c>
       <c r="C4">
-        <v>17.35554749536866</v>
+        <v>17.2524096151109</v>
       </c>
       <c r="D4">
-        <v>17.66274749536866</v>
+        <v>17.7352096151109</v>
       </c>
       <c r="E4">
-        <v>-10.9488</v>
+        <v>-10.7732</v>
       </c>
       <c r="F4">
-        <v>0.3512000000000001</v>
+        <v>0.5268</v>
       </c>
       <c r="G4">
         <v>0.044</v>
@@ -1597,28 +1597,28 @@
         <v>5.074</v>
       </c>
       <c r="M4">
-        <v>0.01766536</v>
+        <v>0.02649804</v>
       </c>
       <c r="N4">
-        <v>5.05633464</v>
+        <v>5.04750196</v>
       </c>
       <c r="O4">
-        <v>1.3652103528</v>
+        <v>1.3628255292</v>
       </c>
       <c r="P4">
-        <v>3.6911242872</v>
+        <v>3.6846764308</v>
       </c>
       <c r="Q4">
-        <v>4.5771242872</v>
+        <v>4.5706764308</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1139345060052865</v>
+        <v>0.1144500548078291</v>
       </c>
       <c r="T4">
-        <v>0.8162338253527915</v>
+        <v>0.8224099671629741</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>287.2287912615424</v>
+        <v>191.4858608410282</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1643,22 +1643,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1121181231635942</v>
+        <v>0.1118460504420077</v>
       </c>
       <c r="C5">
-        <v>17.2524096151109</v>
+        <v>17.14986874151738</v>
       </c>
       <c r="D5">
-        <v>17.7352096151109</v>
+        <v>17.80826874151738</v>
       </c>
       <c r="E5">
-        <v>-10.7732</v>
+        <v>-10.5976</v>
       </c>
       <c r="F5">
-        <v>0.5268</v>
+        <v>0.7024000000000001</v>
       </c>
       <c r="G5">
         <v>0.044</v>
@@ -1679,28 +1679,28 @@
         <v>5.074</v>
       </c>
       <c r="M5">
-        <v>0.02649804</v>
+        <v>0.03533072</v>
       </c>
       <c r="N5">
-        <v>5.04750196</v>
+        <v>5.03866928</v>
       </c>
       <c r="O5">
-        <v>1.3628255292</v>
+        <v>1.3604407056</v>
       </c>
       <c r="P5">
-        <v>3.6846764308</v>
+        <v>3.678228574399999</v>
       </c>
       <c r="Q5">
-        <v>4.5706764308</v>
+        <v>4.5642285744</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1144500548078291</v>
+        <v>0.1149763442104247</v>
       </c>
       <c r="T5">
-        <v>0.8224099671629741</v>
+        <v>0.8287147785942022</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1717,7 +1717,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>191.4858608410282</v>
+        <v>143.6143956307712</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1725,22 +1725,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1118460504420077</v>
+        <v>0.1115739777204211</v>
       </c>
       <c r="C6">
-        <v>17.14986874151738</v>
+        <v>17.04793228310589</v>
       </c>
       <c r="D6">
-        <v>17.80826874151738</v>
+        <v>17.88193228310589</v>
       </c>
       <c r="E6">
-        <v>-10.5976</v>
+        <v>-10.422</v>
       </c>
       <c r="F6">
-        <v>0.7024000000000001</v>
+        <v>0.8780000000000001</v>
       </c>
       <c r="G6">
         <v>0.044</v>
@@ -1761,28 +1761,28 @@
         <v>5.074</v>
       </c>
       <c r="M6">
-        <v>0.03533072</v>
+        <v>0.04416340000000001</v>
       </c>
       <c r="N6">
-        <v>5.03866928</v>
+        <v>5.029836599999999</v>
       </c>
       <c r="O6">
-        <v>1.3604407056</v>
+        <v>1.358055882</v>
       </c>
       <c r="P6">
-        <v>3.678228574399999</v>
+        <v>3.671780717999999</v>
       </c>
       <c r="Q6">
-        <v>4.5642285744</v>
+        <v>4.557780717999999</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1149763442104247</v>
+        <v>0.1155137133899169</v>
       </c>
       <c r="T6">
-        <v>0.8287147785942022</v>
+        <v>0.8351523228976666</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1799,7 +1799,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>143.6143956307712</v>
+        <v>114.8915165046169</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1807,22 +1807,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1115739777204211</v>
+        <v>0.1113019049988346</v>
       </c>
       <c r="C7">
-        <v>17.04793228310589</v>
+        <v>16.94660777148408</v>
       </c>
       <c r="D7">
-        <v>17.88193228310589</v>
+        <v>17.95620777148408</v>
       </c>
       <c r="E7">
-        <v>-10.422</v>
+        <v>-10.2464</v>
       </c>
       <c r="F7">
-        <v>0.8780000000000001</v>
+        <v>1.0536</v>
       </c>
       <c r="G7">
         <v>0.044</v>
@@ -1843,28 +1843,28 @@
         <v>5.074</v>
       </c>
       <c r="M7">
-        <v>0.04416340000000001</v>
+        <v>0.05299608000000001</v>
       </c>
       <c r="N7">
-        <v>5.029836599999999</v>
+        <v>5.02100392</v>
       </c>
       <c r="O7">
-        <v>1.358055882</v>
+        <v>1.3556710584</v>
       </c>
       <c r="P7">
-        <v>3.671780717999999</v>
+        <v>3.6653328616</v>
       </c>
       <c r="Q7">
-        <v>4.557780717999999</v>
+        <v>4.5513328616</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1155137133899169</v>
+        <v>0.116062515956207</v>
       </c>
       <c r="T7">
-        <v>0.8351523228976666</v>
+        <v>0.8417268362288644</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>114.8915165046169</v>
+        <v>95.7429304205141</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1889,22 +1889,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1113019049988346</v>
+        <v>0.111029832277248</v>
       </c>
       <c r="C8">
-        <v>16.94660777148408</v>
+        <v>16.8459028639166</v>
       </c>
       <c r="D8">
-        <v>17.95620777148408</v>
+        <v>18.03110286391659</v>
       </c>
       <c r="E8">
-        <v>-10.2464</v>
+        <v>-10.0708</v>
       </c>
       <c r="F8">
-        <v>1.0536</v>
+        <v>1.2292</v>
       </c>
       <c r="G8">
         <v>0.044</v>
@@ -1925,28 +1925,28 @@
         <v>5.074</v>
       </c>
       <c r="M8">
-        <v>0.05299608</v>
+        <v>0.06182876</v>
       </c>
       <c r="N8">
-        <v>5.02100392</v>
+        <v>5.01217124</v>
       </c>
       <c r="O8">
-        <v>1.3556710584</v>
+        <v>1.3532862348</v>
       </c>
       <c r="P8">
-        <v>3.6653328616</v>
+        <v>3.6588850052</v>
       </c>
       <c r="Q8">
-        <v>4.5513328616</v>
+        <v>4.544885005199999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.116062515956207</v>
+        <v>0.1166231207282236</v>
       </c>
       <c r="T8">
-        <v>0.8417268362288644</v>
+        <v>0.8484427369435287</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>95.74293042051411</v>
+        <v>82.06536893186924</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1971,22 +1971,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.111029832277248</v>
+        <v>0.1107577595556615</v>
       </c>
       <c r="C9">
-        <v>16.8459028639166</v>
+        <v>16.74582534595646</v>
       </c>
       <c r="D9">
-        <v>18.0311028639166</v>
+        <v>18.10662534595646</v>
       </c>
       <c r="E9">
-        <v>-10.0708</v>
+        <v>-9.895200000000001</v>
       </c>
       <c r="F9">
-        <v>1.2292</v>
+        <v>1.4048</v>
       </c>
       <c r="G9">
         <v>0.044</v>
@@ -2007,28 +2007,28 @@
         <v>5.074</v>
       </c>
       <c r="M9">
-        <v>0.06182876000000001</v>
+        <v>0.07066144000000001</v>
       </c>
       <c r="N9">
-        <v>5.01217124</v>
+        <v>5.00333856</v>
       </c>
       <c r="O9">
-        <v>1.3532862348</v>
+        <v>1.3509014112</v>
       </c>
       <c r="P9">
-        <v>3.6588850052</v>
+        <v>3.6524371488</v>
       </c>
       <c r="Q9">
-        <v>4.544885005199999</v>
+        <v>4.5384371488</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1166231207282236</v>
+        <v>0.1171959125605016</v>
       </c>
       <c r="T9">
-        <v>0.8484427369435287</v>
+        <v>0.8553046354998162</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>82.06536893186923</v>
+        <v>71.80719781538558</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2053,22 +2053,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1107577595556615</v>
+        <v>0.1104856868340749</v>
       </c>
       <c r="C10">
-        <v>16.74582534595646</v>
+        <v>16.64638313414319</v>
       </c>
       <c r="D10">
-        <v>18.10662534595646</v>
+        <v>18.18278313414319</v>
       </c>
       <c r="E10">
-        <v>-9.895200000000001</v>
+        <v>-9.7196</v>
       </c>
       <c r="F10">
-        <v>1.4048</v>
+        <v>1.5804</v>
       </c>
       <c r="G10">
         <v>0.044</v>
@@ -2089,28 +2089,28 @@
         <v>5.074</v>
       </c>
       <c r="M10">
-        <v>0.07066144000000001</v>
+        <v>0.07949412000000002</v>
       </c>
       <c r="N10">
-        <v>5.00333856</v>
+        <v>4.99450588</v>
       </c>
       <c r="O10">
-        <v>1.3509014112</v>
+        <v>1.3485165876</v>
       </c>
       <c r="P10">
-        <v>3.6524371488</v>
+        <v>3.6459892924</v>
       </c>
       <c r="Q10">
-        <v>4.5384371488</v>
+        <v>4.5319892924</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1171959125605016</v>
+        <v>0.1177812932242581</v>
       </c>
       <c r="T10">
-        <v>0.8553046354998162</v>
+        <v>0.8623173450133848</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>71.80719781538558</v>
+        <v>63.82862028034274</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2135,22 +2135,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1104856868340749</v>
+        <v>0.1102136141124883</v>
       </c>
       <c r="C11">
-        <v>16.64638313414319</v>
+        <v>16.54758427876901</v>
       </c>
       <c r="D11">
-        <v>18.18278313414319</v>
+        <v>18.25958427876901</v>
       </c>
       <c r="E11">
-        <v>-9.7196</v>
+        <v>-9.544</v>
       </c>
       <c r="F11">
-        <v>1.5804</v>
+        <v>1.756</v>
       </c>
       <c r="G11">
         <v>0.044</v>
@@ -2171,28 +2171,28 @@
         <v>5.074</v>
       </c>
       <c r="M11">
-        <v>0.07949412000000002</v>
+        <v>0.0883268</v>
       </c>
       <c r="N11">
-        <v>4.99450588</v>
+        <v>4.9856732</v>
       </c>
       <c r="O11">
-        <v>1.3485165876</v>
+        <v>1.346131764</v>
       </c>
       <c r="P11">
-        <v>3.6459892924</v>
+        <v>3.639541436</v>
       </c>
       <c r="Q11">
-        <v>4.5319892924</v>
+        <v>4.525541436</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1177812932242581</v>
+        <v>0.1183796823472092</v>
       </c>
       <c r="T11">
-        <v>0.8623173450133848</v>
+        <v>0.8694858925161436</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2209,7 +2209,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>63.82862028034274</v>
+        <v>57.44575825230847</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2217,22 +2217,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1102136141124883</v>
+        <v>0.1099415413909018</v>
       </c>
       <c r="C12">
-        <v>16.54758427876901</v>
+        <v>16.44943696671561</v>
       </c>
       <c r="D12">
-        <v>18.25958427876901</v>
+        <v>18.33703696671561</v>
       </c>
       <c r="E12">
-        <v>-9.544</v>
+        <v>-9.368400000000001</v>
       </c>
       <c r="F12">
-        <v>1.756</v>
+        <v>1.9316</v>
       </c>
       <c r="G12">
         <v>0.044</v>
@@ -2253,28 +2253,28 @@
         <v>5.074</v>
       </c>
       <c r="M12">
-        <v>0.08832680000000001</v>
+        <v>0.09715948000000001</v>
       </c>
       <c r="N12">
-        <v>4.9856732</v>
+        <v>4.97684052</v>
       </c>
       <c r="O12">
-        <v>1.346131764</v>
+        <v>1.3437469404</v>
       </c>
       <c r="P12">
-        <v>3.639541436</v>
+        <v>3.6330935796</v>
       </c>
       <c r="Q12">
-        <v>4.525541436</v>
+        <v>4.5190935796</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1183796823472092</v>
+        <v>0.1189915184167436</v>
       </c>
       <c r="T12">
-        <v>0.8694858925161436</v>
+        <v>0.8768155309740208</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>57.44575825230847</v>
+        <v>52.2234165930077</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2299,22 +2299,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1099415413909018</v>
+        <v>0.1096694686693152</v>
       </c>
       <c r="C13">
-        <v>16.44943696671561</v>
+        <v>16.35194952436343</v>
       </c>
       <c r="D13">
-        <v>18.33703696671561</v>
+        <v>18.41514952436343</v>
       </c>
       <c r="E13">
-        <v>-9.368400000000001</v>
+        <v>-9.1928</v>
       </c>
       <c r="F13">
-        <v>1.9316</v>
+        <v>2.1072</v>
       </c>
       <c r="G13">
         <v>0.044</v>
@@ -2335,28 +2335,28 @@
         <v>5.074</v>
       </c>
       <c r="M13">
-        <v>0.09715948000000001</v>
+        <v>0.10599216</v>
       </c>
       <c r="N13">
-        <v>4.97684052</v>
+        <v>4.96800784</v>
       </c>
       <c r="O13">
-        <v>1.3437469404</v>
+        <v>1.3413621168</v>
       </c>
       <c r="P13">
-        <v>3.6330935796</v>
+        <v>3.6266457232</v>
       </c>
       <c r="Q13">
-        <v>4.5190935796</v>
+        <v>4.5126457232</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1189915184167436</v>
+        <v>0.1196172598514946</v>
       </c>
       <c r="T13">
-        <v>0.8768155309740208</v>
+        <v>0.8843117521241224</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>52.2234165930077</v>
+        <v>47.87146521025706</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2381,22 +2381,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1096694686693152</v>
+        <v>0.1093973959477287</v>
       </c>
       <c r="C14">
-        <v>16.35194952436343</v>
+        <v>16.25513042057552</v>
       </c>
       <c r="D14">
-        <v>18.41514952436343</v>
+        <v>18.49393042057552</v>
       </c>
       <c r="E14">
-        <v>-9.1928</v>
+        <v>-9.017200000000001</v>
       </c>
       <c r="F14">
-        <v>2.1072</v>
+        <v>2.2828</v>
       </c>
       <c r="G14">
         <v>0.044</v>
@@ -2417,28 +2417,28 @@
         <v>5.074</v>
       </c>
       <c r="M14">
-        <v>0.10599216</v>
+        <v>0.11482484</v>
       </c>
       <c r="N14">
-        <v>4.96800784</v>
+        <v>4.95917516</v>
       </c>
       <c r="O14">
-        <v>1.3413621168</v>
+        <v>1.3389772932</v>
       </c>
       <c r="P14">
-        <v>3.6266457232</v>
+        <v>3.6201978668</v>
       </c>
       <c r="Q14">
-        <v>4.5126457232</v>
+        <v>4.5061978668</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1196172598514946</v>
+        <v>0.1202573861468146</v>
       </c>
       <c r="T14">
-        <v>0.8843117521241224</v>
+        <v>0.8919803001972147</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>47.87146521025706</v>
+        <v>44.18904480946805</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2463,22 +2463,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1093973959477287</v>
+        <v>0.1091253232261421</v>
       </c>
       <c r="C15">
-        <v>16.25513042057552</v>
+        <v>16.15898826975837</v>
       </c>
       <c r="D15">
-        <v>18.49393042057552</v>
+        <v>18.57338826975837</v>
       </c>
       <c r="E15">
-        <v>-9.017200000000001</v>
+        <v>-8.8416</v>
       </c>
       <c r="F15">
-        <v>2.2828</v>
+        <v>2.458400000000001</v>
       </c>
       <c r="G15">
         <v>0.044</v>
@@ -2499,28 +2499,28 @@
         <v>5.074</v>
       </c>
       <c r="M15">
-        <v>0.11482484</v>
+        <v>0.12365752</v>
       </c>
       <c r="N15">
-        <v>4.95917516</v>
+        <v>4.95034248</v>
       </c>
       <c r="O15">
-        <v>1.3389772932</v>
+        <v>1.3365924696</v>
       </c>
       <c r="P15">
-        <v>3.6201978668</v>
+        <v>3.6137500104</v>
       </c>
       <c r="Q15">
-        <v>4.5061978668</v>
+        <v>4.4997500104</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1202573861468146</v>
+        <v>0.1209123991001652</v>
       </c>
       <c r="T15">
-        <v>0.8919803001972147</v>
+        <v>0.8998271865975884</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2537,7 +2537,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>44.18904480946805</v>
+        <v>41.03268446593462</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2545,22 +2545,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1091253232261421</v>
+        <v>0.1088532505045555</v>
       </c>
       <c r="C16">
-        <v>16.15898826975837</v>
+        <v>16.06353183500205</v>
       </c>
       <c r="D16">
-        <v>18.57338826975837</v>
+        <v>18.65353183500205</v>
       </c>
       <c r="E16">
-        <v>-8.8416</v>
+        <v>-8.666</v>
       </c>
       <c r="F16">
-        <v>2.458400000000001</v>
+        <v>2.634000000000001</v>
       </c>
       <c r="G16">
         <v>0.044</v>
@@ -2581,28 +2581,28 @@
         <v>5.074</v>
       </c>
       <c r="M16">
-        <v>0.12365752</v>
+        <v>0.1324902</v>
       </c>
       <c r="N16">
-        <v>4.95034248</v>
+        <v>4.9415098</v>
       </c>
       <c r="O16">
-        <v>1.3365924696</v>
+        <v>1.334207646</v>
       </c>
       <c r="P16">
-        <v>3.6137500104</v>
+        <v>3.607302154</v>
       </c>
       <c r="Q16">
-        <v>4.4997500104</v>
+        <v>4.493302153999999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1209123991001652</v>
+        <v>0.1215828241230065</v>
       </c>
       <c r="T16">
-        <v>0.8998271865975884</v>
+        <v>0.9078587056191474</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>41.03268446593462</v>
+        <v>38.29717216820563</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1088532505045555</v>
+        <v>0.108581177782969</v>
       </c>
       <c r="C17">
-        <v>16.06353183500205</v>
+        <v>15.9687700313018</v>
       </c>
       <c r="D17">
-        <v>18.65353183500205</v>
+        <v>18.7343700313018</v>
       </c>
       <c r="E17">
-        <v>-8.666</v>
+        <v>-8.490400000000001</v>
       </c>
       <c r="F17">
-        <v>2.634</v>
+        <v>2.809600000000001</v>
       </c>
       <c r="G17">
         <v>0.044</v>
@@ -2663,28 +2663,28 @@
         <v>5.074</v>
       </c>
       <c r="M17">
-        <v>0.1324902</v>
+        <v>0.14132288</v>
       </c>
       <c r="N17">
-        <v>4.9415098</v>
+        <v>4.93267712</v>
       </c>
       <c r="O17">
-        <v>1.334207646</v>
+        <v>1.3318228224</v>
       </c>
       <c r="P17">
-        <v>3.607302154</v>
+        <v>3.6008542976</v>
       </c>
       <c r="Q17">
-        <v>4.493302153999999</v>
+        <v>4.4868542976</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1215828241230065</v>
+        <v>0.1222692116463917</v>
       </c>
       <c r="T17">
-        <v>0.9078587056191474</v>
+        <v>0.9160814512840768</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>38.29717216820564</v>
+        <v>35.9035989076928</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2709,22 +2709,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.108581177782969</v>
+        <v>0.1083091050613825</v>
       </c>
       <c r="C18">
-        <v>15.9687700313018</v>
+        <v>15.8747119288641</v>
       </c>
       <c r="D18">
-        <v>18.7343700313018</v>
+        <v>18.8159119288641</v>
       </c>
       <c r="E18">
-        <v>-8.490400000000001</v>
+        <v>-8.3148</v>
       </c>
       <c r="F18">
-        <v>2.809600000000001</v>
+        <v>2.985200000000001</v>
       </c>
       <c r="G18">
         <v>0.044</v>
@@ -2745,28 +2745,28 @@
         <v>5.074</v>
       </c>
       <c r="M18">
-        <v>0.14132288</v>
+        <v>0.15015556</v>
       </c>
       <c r="N18">
-        <v>4.93267712</v>
+        <v>4.92384444</v>
       </c>
       <c r="O18">
-        <v>1.3318228224</v>
+        <v>1.3294379988</v>
       </c>
       <c r="P18">
-        <v>3.6008542976</v>
+        <v>3.5944064412</v>
       </c>
       <c r="Q18">
-        <v>4.4868542976</v>
+        <v>4.4804064412</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1222692116463917</v>
+        <v>0.1229721386281716</v>
       </c>
       <c r="T18">
-        <v>0.9160814512840768</v>
+        <v>0.9245023353987635</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>35.9035989076928</v>
+        <v>33.79162250135792</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2791,22 +2791,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1083091050613825</v>
+        <v>0.1080370323397959</v>
       </c>
       <c r="C19">
-        <v>15.8747119288641</v>
+        <v>15.78136675649902</v>
       </c>
       <c r="D19">
-        <v>18.8159119288641</v>
+        <v>18.89816675649902</v>
       </c>
       <c r="E19">
-        <v>-8.3148</v>
+        <v>-8.139199999999999</v>
       </c>
       <c r="F19">
-        <v>2.985200000000001</v>
+        <v>3.160800000000001</v>
       </c>
       <c r="G19">
         <v>0.044</v>
@@ -2827,28 +2827,28 @@
         <v>5.074</v>
       </c>
       <c r="M19">
-        <v>0.15015556</v>
+        <v>0.15898824</v>
       </c>
       <c r="N19">
-        <v>4.92384444</v>
+        <v>4.91501176</v>
       </c>
       <c r="O19">
-        <v>1.3294379988</v>
+        <v>1.3270531752</v>
       </c>
       <c r="P19">
-        <v>3.5944064412</v>
+        <v>3.5879585848</v>
       </c>
       <c r="Q19">
-        <v>4.4804064412</v>
+        <v>4.4739585848</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1229721386281716</v>
+        <v>0.1236922101704828</v>
       </c>
       <c r="T19">
-        <v>0.9245023353987635</v>
+        <v>0.9331286069308815</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2865,7 +2865,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>33.79162250135792</v>
+        <v>31.91431014017137</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2873,22 +2873,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1080370323397959</v>
+        <v>0.1077649596182093</v>
       </c>
       <c r="C20">
-        <v>15.78136675649902</v>
+        <v>15.68874390510231</v>
       </c>
       <c r="D20">
-        <v>18.89816675649902</v>
+        <v>18.98114390510231</v>
       </c>
       <c r="E20">
-        <v>-8.139200000000001</v>
+        <v>-7.9636</v>
       </c>
       <c r="F20">
-        <v>3.1608</v>
+        <v>3.3364</v>
       </c>
       <c r="G20">
         <v>0.044</v>
@@ -2909,28 +2909,28 @@
         <v>5.074</v>
       </c>
       <c r="M20">
-        <v>0.15898824</v>
+        <v>0.16782092</v>
       </c>
       <c r="N20">
-        <v>4.91501176</v>
+        <v>4.90617908</v>
       </c>
       <c r="O20">
-        <v>1.3270531752</v>
+        <v>1.3246683516</v>
       </c>
       <c r="P20">
-        <v>3.5879585848</v>
+        <v>3.5815107284</v>
       </c>
       <c r="Q20">
-        <v>4.4739585848</v>
+        <v>4.4675107284</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1236922101704828</v>
+        <v>0.1244300612570486</v>
       </c>
       <c r="T20">
-        <v>0.9331286069308815</v>
+        <v>0.9419678728218174</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2947,7 +2947,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>31.91431014017137</v>
+        <v>30.23460960647814</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2955,22 +2955,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1077649596182093</v>
+        <v>0.1074928868966228</v>
       </c>
       <c r="C21">
-        <v>15.68874390510231</v>
+        <v>15.59685293122944</v>
       </c>
       <c r="D21">
-        <v>18.98114390510231</v>
+        <v>19.06485293122944</v>
       </c>
       <c r="E21">
-        <v>-7.9636</v>
+        <v>-7.788</v>
       </c>
       <c r="F21">
-        <v>3.3364</v>
+        <v>3.512</v>
       </c>
       <c r="G21">
         <v>0.044</v>
@@ -2991,28 +2991,28 @@
         <v>5.074</v>
       </c>
       <c r="M21">
-        <v>0.16782092</v>
+        <v>0.1766536</v>
       </c>
       <c r="N21">
-        <v>4.90617908</v>
+        <v>4.8973464</v>
       </c>
       <c r="O21">
-        <v>1.3246683516</v>
+        <v>1.322283528</v>
       </c>
       <c r="P21">
-        <v>3.5815107284</v>
+        <v>3.575062872</v>
       </c>
       <c r="Q21">
-        <v>4.4675107284</v>
+        <v>4.461062872</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1244300612570486</v>
+        <v>0.1251863586207785</v>
       </c>
       <c r="T21">
-        <v>0.9419678728218174</v>
+        <v>0.9510281203600267</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3029,7 +3029,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>30.23460960647814</v>
+        <v>28.72287912615423</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3037,22 +3037,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1074928868966228</v>
+        <v>0.1072208141750362</v>
       </c>
       <c r="C22">
-        <v>15.59685293122944</v>
+        <v>15.50570356076465</v>
       </c>
       <c r="D22">
-        <v>19.06485293122944</v>
+        <v>19.14930356076465</v>
       </c>
       <c r="E22">
-        <v>-7.788</v>
+        <v>-7.6124</v>
       </c>
       <c r="F22">
-        <v>3.512</v>
+        <v>3.687600000000001</v>
       </c>
       <c r="G22">
         <v>0.044</v>
@@ -3073,28 +3073,28 @@
         <v>5.074</v>
       </c>
       <c r="M22">
-        <v>0.1766536</v>
+        <v>0.18548628</v>
       </c>
       <c r="N22">
-        <v>4.8973464</v>
+        <v>4.88851372</v>
       </c>
       <c r="O22">
-        <v>1.322283528</v>
+        <v>1.3198987044</v>
       </c>
       <c r="P22">
-        <v>3.575062872</v>
+        <v>3.5686150156</v>
       </c>
       <c r="Q22">
-        <v>4.461062872</v>
+        <v>4.4546150156</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1251863586207785</v>
+        <v>0.1259618027532104</v>
       </c>
       <c r="T22">
-        <v>0.9510281203600267</v>
+        <v>0.9603177412536336</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>28.72287912615423</v>
+        <v>27.35512297728974</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3119,22 +3119,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1072208141750362</v>
+        <v>0.1069487414534497</v>
       </c>
       <c r="C23">
-        <v>15.50570356076465</v>
+        <v>15.41530569268801</v>
       </c>
       <c r="D23">
-        <v>19.14930356076465</v>
+        <v>19.23450569268801</v>
       </c>
       <c r="E23">
-        <v>-7.612400000000001</v>
+        <v>-7.4368</v>
       </c>
       <c r="F23">
-        <v>3.6876</v>
+        <v>3.8632</v>
       </c>
       <c r="G23">
         <v>0.044</v>
@@ -3155,28 +3155,28 @@
         <v>5.074</v>
       </c>
       <c r="M23">
-        <v>0.18548628</v>
+        <v>0.19431896</v>
       </c>
       <c r="N23">
-        <v>4.88851372</v>
+        <v>4.879681039999999</v>
       </c>
       <c r="O23">
-        <v>1.3198987044</v>
+        <v>1.3175138808</v>
       </c>
       <c r="P23">
-        <v>3.5686150156</v>
+        <v>3.562167159199999</v>
       </c>
       <c r="Q23">
-        <v>4.4546150156</v>
+        <v>4.4481671592</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1259618027532104</v>
+        <v>0.1267571300685252</v>
       </c>
       <c r="T23">
-        <v>0.9603177412536336</v>
+        <v>0.9698455575547688</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3193,7 +3193,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>27.35512297728975</v>
+        <v>26.11170829650385</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3201,22 +3201,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1069487414534497</v>
+        <v>0.1066766687318631</v>
       </c>
       <c r="C24">
-        <v>15.41530569268801</v>
+        <v>15.32566940294344</v>
       </c>
       <c r="D24">
-        <v>19.23450569268801</v>
+        <v>19.32046940294344</v>
       </c>
       <c r="E24">
-        <v>-7.4368</v>
+        <v>-7.2612</v>
       </c>
       <c r="F24">
-        <v>3.8632</v>
+        <v>4.038800000000001</v>
       </c>
       <c r="G24">
         <v>0.044</v>
@@ -3237,28 +3237,28 @@
         <v>5.074</v>
       </c>
       <c r="M24">
-        <v>0.19431896</v>
+        <v>0.20315164</v>
       </c>
       <c r="N24">
-        <v>4.879681039999999</v>
+        <v>4.87084836</v>
       </c>
       <c r="O24">
-        <v>1.3175138808</v>
+        <v>1.3151290572</v>
       </c>
       <c r="P24">
-        <v>3.562167159199999</v>
+        <v>3.5557193028</v>
       </c>
       <c r="Q24">
-        <v>4.4481671592</v>
+        <v>4.4417193028</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1267571300685252</v>
+        <v>0.1275731152361859</v>
       </c>
       <c r="T24">
-        <v>0.9698455575547688</v>
+        <v>0.9796208496039855</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3275,7 +3275,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>26.11170829650385</v>
+        <v>24.97641663143846</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3283,22 +3283,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1066766687318631</v>
+        <v>0.1064045960102766</v>
       </c>
       <c r="C25">
-        <v>15.32566940294344</v>
+        <v>15.23680494841094</v>
       </c>
       <c r="D25">
-        <v>19.32046940294344</v>
+        <v>19.40720494841094</v>
       </c>
       <c r="E25">
-        <v>-7.2612</v>
+        <v>-7.085599999999999</v>
       </c>
       <c r="F25">
-        <v>4.038800000000001</v>
+        <v>4.214400000000001</v>
       </c>
       <c r="G25">
         <v>0.044</v>
@@ -3319,28 +3319,28 @@
         <v>5.074</v>
       </c>
       <c r="M25">
-        <v>0.20315164</v>
+        <v>0.2119843200000001</v>
       </c>
       <c r="N25">
-        <v>4.87084836</v>
+        <v>4.86201568</v>
       </c>
       <c r="O25">
-        <v>1.3151290572</v>
+        <v>1.3127442336</v>
       </c>
       <c r="P25">
-        <v>3.5557193028</v>
+        <v>3.5492714464</v>
       </c>
       <c r="Q25">
-        <v>4.4417193028</v>
+        <v>4.4352714464</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1275731152361859</v>
+        <v>0.1284105736977323</v>
       </c>
       <c r="T25">
-        <v>0.9796208496039855</v>
+        <v>0.9896533861808132</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3357,7 +3357,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>24.97641663143846</v>
+        <v>23.93573260512852</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3365,22 +3365,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1064045960102766</v>
+        <v>0.10613252328869</v>
       </c>
       <c r="C26">
-        <v>15.23680494841094</v>
+        <v>15.14872277098628</v>
       </c>
       <c r="D26">
-        <v>19.40720494841094</v>
+        <v>19.49472277098628</v>
       </c>
       <c r="E26">
-        <v>-7.0856</v>
+        <v>-6.91</v>
       </c>
       <c r="F26">
-        <v>4.2144</v>
+        <v>4.390000000000001</v>
       </c>
       <c r="G26">
         <v>0.044</v>
@@ -3401,28 +3401,28 @@
         <v>5.074</v>
       </c>
       <c r="M26">
-        <v>0.21198432</v>
+        <v>0.220817</v>
       </c>
       <c r="N26">
-        <v>4.86201568</v>
+        <v>4.853183</v>
       </c>
       <c r="O26">
-        <v>1.3127442336</v>
+        <v>1.31035941</v>
       </c>
       <c r="P26">
-        <v>3.5492714464</v>
+        <v>3.542823589999999</v>
       </c>
       <c r="Q26">
-        <v>4.4352714464</v>
+        <v>4.428823589999999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1284105736977323</v>
+        <v>0.12927036438492</v>
       </c>
       <c r="T26">
-        <v>0.9896533861808132</v>
+        <v>0.9999534570663564</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3439,7 +3439,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>23.93573260512853</v>
+        <v>22.97830330092339</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3447,22 +3447,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.10613252328869</v>
+        <v>0.1058604505671035</v>
       </c>
       <c r="C27">
-        <v>15.14872277098628</v>
+        <v>15.06143350177162</v>
       </c>
       <c r="D27">
-        <v>19.49472277098628</v>
+        <v>19.58303350177162</v>
       </c>
       <c r="E27">
-        <v>-6.91</v>
+        <v>-6.7344</v>
       </c>
       <c r="F27">
-        <v>4.390000000000001</v>
+        <v>4.565600000000001</v>
       </c>
       <c r="G27">
         <v>0.044</v>
@@ -3483,28 +3483,28 @@
         <v>5.074</v>
       </c>
       <c r="M27">
-        <v>0.220817</v>
+        <v>0.22964968</v>
       </c>
       <c r="N27">
-        <v>4.853183</v>
+        <v>4.84435032</v>
       </c>
       <c r="O27">
-        <v>1.31035941</v>
+        <v>1.3079745864</v>
       </c>
       <c r="P27">
-        <v>3.542823589999999</v>
+        <v>3.5363757336</v>
       </c>
       <c r="Q27">
-        <v>4.428823589999999</v>
+        <v>4.4223757336</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.12927036438492</v>
+        <v>0.1301533926582479</v>
       </c>
       <c r="T27">
-        <v>0.9999534570663564</v>
+        <v>1.010531908246103</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>22.97830330092339</v>
+        <v>22.09452240473403</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3529,22 +3529,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1058604505671035</v>
+        <v>0.1055883778455169</v>
       </c>
       <c r="C28">
-        <v>15.06143350177162</v>
+        <v>14.97494796538049</v>
       </c>
       <c r="D28">
-        <v>19.58303350177162</v>
+        <v>19.67214796538049</v>
       </c>
       <c r="E28">
-        <v>-6.7344</v>
+        <v>-6.5588</v>
       </c>
       <c r="F28">
-        <v>4.565600000000001</v>
+        <v>4.741200000000001</v>
       </c>
       <c r="G28">
         <v>0.044</v>
@@ -3565,28 +3565,28 @@
         <v>5.074</v>
       </c>
       <c r="M28">
-        <v>0.22964968</v>
+        <v>0.23848236</v>
       </c>
       <c r="N28">
-        <v>4.84435032</v>
+        <v>4.83551764</v>
       </c>
       <c r="O28">
-        <v>1.3079745864</v>
+        <v>1.3055897628</v>
       </c>
       <c r="P28">
-        <v>3.5363757336</v>
+        <v>3.5299278772</v>
       </c>
       <c r="Q28">
-        <v>4.4223757336</v>
+        <v>4.4159278772</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1301533926582479</v>
+        <v>0.1310606134870095</v>
       </c>
       <c r="T28">
-        <v>1.010531908246103</v>
+        <v>1.021400180006117</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>22.09452240473403</v>
+        <v>21.27620676011425</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3611,22 +3611,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1055883778455169</v>
+        <v>0.1053163051239303</v>
       </c>
       <c r="C29">
-        <v>14.97494796538049</v>
+        <v>14.8892771843609</v>
       </c>
       <c r="D29">
-        <v>19.67214796538049</v>
+        <v>19.7620771843609</v>
       </c>
       <c r="E29">
-        <v>-6.5588</v>
+        <v>-6.3832</v>
       </c>
       <c r="F29">
-        <v>4.741200000000001</v>
+        <v>4.916800000000001</v>
       </c>
       <c r="G29">
         <v>0.044</v>
@@ -3647,28 +3647,28 @@
         <v>5.074</v>
       </c>
       <c r="M29">
-        <v>0.23848236</v>
+        <v>0.24731504</v>
       </c>
       <c r="N29">
-        <v>4.83551764</v>
+        <v>4.82668496</v>
       </c>
       <c r="O29">
-        <v>1.3055897628</v>
+        <v>1.3032049392</v>
       </c>
       <c r="P29">
-        <v>3.5299278772</v>
+        <v>3.5234800208</v>
       </c>
       <c r="Q29">
-        <v>4.4159278772</v>
+        <v>4.409480020799999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1310606134870095</v>
+        <v>0.1319930348943477</v>
       </c>
       <c r="T29">
-        <v>1.021400180006117</v>
+        <v>1.032570348203909</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>21.27620676011425</v>
+        <v>20.51634223296731</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1053163051239303</v>
+        <v>0.1050442324023438</v>
       </c>
       <c r="C30">
-        <v>14.8892771843609</v>
+        <v>14.80443238374027</v>
       </c>
       <c r="D30">
-        <v>19.7620771843609</v>
+        <v>19.85283238374027</v>
       </c>
       <c r="E30">
-        <v>-6.3832</v>
+        <v>-6.207599999999999</v>
       </c>
       <c r="F30">
-        <v>4.916800000000001</v>
+        <v>5.092400000000001</v>
       </c>
       <c r="G30">
         <v>0.044</v>
@@ -3729,28 +3729,28 @@
         <v>5.074</v>
       </c>
       <c r="M30">
-        <v>0.24731504</v>
+        <v>0.2561477200000001</v>
       </c>
       <c r="N30">
-        <v>4.82668496</v>
+        <v>4.817852279999999</v>
       </c>
       <c r="O30">
-        <v>1.3032049392</v>
+        <v>1.3008201156</v>
       </c>
       <c r="P30">
-        <v>3.5234800208</v>
+        <v>3.5170321644</v>
       </c>
       <c r="Q30">
-        <v>4.409480020799999</v>
+        <v>4.4030321644</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1319930348943477</v>
+        <v>0.1329517216934419</v>
       </c>
       <c r="T30">
-        <v>1.032570348203909</v>
+        <v>1.044055169026992</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3767,7 +3767,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>20.51634223296731</v>
+        <v>19.80888215596843</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3775,22 +3775,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1050442324023438</v>
+        <v>0.1047721596807572</v>
       </c>
       <c r="C31">
-        <v>14.80443238374027</v>
+        <v>14.72042499569626</v>
       </c>
       <c r="D31">
-        <v>19.85283238374027</v>
+        <v>19.94442499569626</v>
       </c>
       <c r="E31">
-        <v>-6.2076</v>
+        <v>-6.032</v>
       </c>
       <c r="F31">
-        <v>5.0924</v>
+        <v>5.268000000000001</v>
       </c>
       <c r="G31">
         <v>0.044</v>
@@ -3811,28 +3811,28 @@
         <v>5.074</v>
       </c>
       <c r="M31">
-        <v>0.25614772</v>
+        <v>0.2649804</v>
       </c>
       <c r="N31">
-        <v>4.817852279999999</v>
+        <v>4.8090196</v>
       </c>
       <c r="O31">
-        <v>1.3008201156</v>
+        <v>1.298435292</v>
       </c>
       <c r="P31">
-        <v>3.5170321644</v>
+        <v>3.510584308</v>
       </c>
       <c r="Q31">
-        <v>4.4030321644</v>
+        <v>4.396584308</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1329517216934419</v>
+        <v>0.1339377995439389</v>
       </c>
       <c r="T31">
-        <v>1.044055169026992</v>
+        <v>1.055868127587876</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>19.80888215596843</v>
+        <v>19.14858608410282</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3857,22 +3857,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1047721596807572</v>
+        <v>0.1045000869591707</v>
       </c>
       <c r="C32">
-        <v>14.72042499569626</v>
+        <v>14.63726666435737</v>
       </c>
       <c r="D32">
-        <v>19.94442499569626</v>
+        <v>20.03686666435737</v>
       </c>
       <c r="E32">
-        <v>-6.032</v>
+        <v>-5.8564</v>
       </c>
       <c r="F32">
-        <v>5.268000000000001</v>
+        <v>5.443600000000001</v>
       </c>
       <c r="G32">
         <v>0.044</v>
@@ -3893,28 +3893,28 @@
         <v>5.074</v>
       </c>
       <c r="M32">
-        <v>0.2649804</v>
+        <v>0.27381308</v>
       </c>
       <c r="N32">
-        <v>4.8090196</v>
+        <v>4.80018692</v>
       </c>
       <c r="O32">
-        <v>1.298435292</v>
+        <v>1.2960504684</v>
       </c>
       <c r="P32">
-        <v>3.510584308</v>
+        <v>3.5041364516</v>
       </c>
       <c r="Q32">
-        <v>4.396584308</v>
+        <v>4.3901364516</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1339377995439389</v>
+        <v>0.1349524593611169</v>
       </c>
       <c r="T32">
-        <v>1.055868127587876</v>
+        <v>1.068023490744728</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3931,7 +3931,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>19.14858608410282</v>
+        <v>18.53088975880918</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3939,22 +3939,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1045000869591707</v>
+        <v>0.1042280142375841</v>
       </c>
       <c r="C33">
-        <v>14.63726666435737</v>
+        <v>14.55496925073779</v>
       </c>
       <c r="D33">
-        <v>20.03686666435737</v>
+        <v>20.13016925073779</v>
       </c>
       <c r="E33">
-        <v>-5.8564</v>
+        <v>-5.6808</v>
       </c>
       <c r="F33">
-        <v>5.443600000000001</v>
+        <v>5.619200000000001</v>
       </c>
       <c r="G33">
         <v>0.044</v>
@@ -3975,28 +3975,28 @@
         <v>5.074</v>
       </c>
       <c r="M33">
-        <v>0.27381308</v>
+        <v>0.28264576</v>
       </c>
       <c r="N33">
-        <v>4.80018692</v>
+        <v>4.79135424</v>
       </c>
       <c r="O33">
-        <v>1.2960504684</v>
+        <v>1.2936656448</v>
       </c>
       <c r="P33">
-        <v>3.5041364516</v>
+        <v>3.4976885952</v>
       </c>
       <c r="Q33">
-        <v>4.3901364516</v>
+        <v>4.3836885952</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1349524593611169</v>
+        <v>0.1359969621140943</v>
       </c>
       <c r="T33">
-        <v>1.068023490744728</v>
+        <v>1.080536364582664</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4013,7 +4013,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>18.53088975880918</v>
+        <v>17.95179945384639</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4021,22 +4021,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1042280142375841</v>
+        <v>0.1039559415159976</v>
       </c>
       <c r="C34">
-        <v>14.55496925073779</v>
+        <v>14.47354483781068</v>
       </c>
       <c r="D34">
-        <v>20.13016925073779</v>
+        <v>20.22434483781068</v>
       </c>
       <c r="E34">
-        <v>-5.6808</v>
+        <v>-5.505199999999999</v>
       </c>
       <c r="F34">
-        <v>5.619200000000001</v>
+        <v>5.794800000000001</v>
       </c>
       <c r="G34">
         <v>0.044</v>
@@ -4057,28 +4057,28 @@
         <v>5.074</v>
       </c>
       <c r="M34">
-        <v>0.28264576</v>
+        <v>0.2914784400000001</v>
       </c>
       <c r="N34">
-        <v>4.79135424</v>
+        <v>4.78252156</v>
       </c>
       <c r="O34">
-        <v>1.2936656448</v>
+        <v>1.2912808212</v>
       </c>
       <c r="P34">
-        <v>3.4976885952</v>
+        <v>3.4912407388</v>
       </c>
       <c r="Q34">
-        <v>4.3836885952</v>
+        <v>4.3772407388</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1359969621140943</v>
+        <v>0.1370726440537277</v>
       </c>
       <c r="T34">
-        <v>1.080536364582664</v>
+        <v>1.093422757042628</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4095,7 +4095,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>17.95179945384639</v>
+        <v>17.40780553100257</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4103,22 +4103,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1039559415159976</v>
+        <v>0.103683868794411</v>
       </c>
       <c r="C35">
-        <v>14.47354483781068</v>
+        <v>14.39300573572461</v>
       </c>
       <c r="D35">
-        <v>20.22434483781068</v>
+        <v>20.31940573572461</v>
       </c>
       <c r="E35">
-        <v>-5.505199999999999</v>
+        <v>-5.329599999999999</v>
       </c>
       <c r="F35">
-        <v>5.794800000000001</v>
+        <v>5.970400000000001</v>
       </c>
       <c r="G35">
         <v>0.044</v>
@@ -4139,28 +4139,28 @@
         <v>5.074</v>
       </c>
       <c r="M35">
-        <v>0.2914784400000001</v>
+        <v>0.30031112</v>
       </c>
       <c r="N35">
-        <v>4.78252156</v>
+        <v>4.77368888</v>
       </c>
       <c r="O35">
-        <v>1.2912808212</v>
+        <v>1.2888959976</v>
       </c>
       <c r="P35">
-        <v>3.4912407388</v>
+        <v>3.4847928824</v>
       </c>
       <c r="Q35">
-        <v>4.3772407388</v>
+        <v>4.3707928824</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1370726440537277</v>
+        <v>0.1381809224157742</v>
       </c>
       <c r="T35">
-        <v>1.093422757042628</v>
+        <v>1.106699646243803</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4177,7 +4177,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>17.40780553100257</v>
+        <v>16.89581125067896</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4185,22 +4185,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.103683868794411</v>
+        <v>0.1034117960728244</v>
       </c>
       <c r="C36">
-        <v>14.39300573572461</v>
+        <v>14.31336448716766</v>
       </c>
       <c r="D36">
-        <v>20.31940573572461</v>
+        <v>20.41536448716766</v>
       </c>
       <c r="E36">
-        <v>-5.329599999999999</v>
+        <v>-5.153999999999999</v>
       </c>
       <c r="F36">
-        <v>5.970400000000001</v>
+        <v>6.146000000000002</v>
       </c>
       <c r="G36">
         <v>0.044</v>
@@ -4221,28 +4221,28 @@
         <v>5.074</v>
       </c>
       <c r="M36">
-        <v>0.30031112</v>
+        <v>0.3091438000000001</v>
       </c>
       <c r="N36">
-        <v>4.77368888</v>
+        <v>4.7648562</v>
       </c>
       <c r="O36">
-        <v>1.2888959976</v>
+        <v>1.286511174</v>
       </c>
       <c r="P36">
-        <v>3.4847928824</v>
+        <v>3.478345026</v>
       </c>
       <c r="Q36">
-        <v>4.3707928824</v>
+        <v>4.364345026</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1381809224157742</v>
+        <v>0.1393233016504992</v>
       </c>
       <c r="T36">
-        <v>1.106699646243803</v>
+        <v>1.120385055112707</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4259,7 +4259,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>16.89581125067896</v>
+        <v>16.41307378637384</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4267,22 +4267,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1034117960728244</v>
+        <v>0.1031397233512379</v>
       </c>
       <c r="C37">
-        <v>14.31336448716766</v>
+        <v>14.23463387288445</v>
       </c>
       <c r="D37">
-        <v>20.41536448716766</v>
+        <v>20.51223387288445</v>
       </c>
       <c r="E37">
-        <v>-5.153999999999999</v>
+        <v>-4.978399999999999</v>
       </c>
       <c r="F37">
-        <v>6.146000000000002</v>
+        <v>6.321600000000002</v>
       </c>
       <c r="G37">
         <v>0.044</v>
@@ -4303,28 +4303,28 @@
         <v>5.074</v>
       </c>
       <c r="M37">
-        <v>0.3091438000000001</v>
+        <v>0.3179764800000001</v>
       </c>
       <c r="N37">
-        <v>4.7648562</v>
+        <v>4.756023519999999</v>
       </c>
       <c r="O37">
-        <v>1.286511174</v>
+        <v>1.2841263504</v>
       </c>
       <c r="P37">
-        <v>3.478345026</v>
+        <v>3.471897169599999</v>
       </c>
       <c r="Q37">
-        <v>4.364345026</v>
+        <v>4.357897169599999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1393233016504992</v>
+        <v>0.1405013802363092</v>
       </c>
       <c r="T37">
-        <v>1.120385055112707</v>
+        <v>1.134498133008763</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4341,7 +4341,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>16.41307378637384</v>
+        <v>15.95715507008568</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4349,22 +4349,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1031397233512379</v>
+        <v>0.1028676506296513</v>
       </c>
       <c r="C38">
-        <v>14.23463387288445</v>
+        <v>14.1568269173508</v>
       </c>
       <c r="D38">
-        <v>20.51223387288445</v>
+        <v>20.6100269173508</v>
       </c>
       <c r="E38">
-        <v>-4.9784</v>
+        <v>-4.8028</v>
       </c>
       <c r="F38">
-        <v>6.321600000000001</v>
+        <v>6.497200000000001</v>
       </c>
       <c r="G38">
         <v>0.044</v>
@@ -4385,28 +4385,28 @@
         <v>5.074</v>
       </c>
       <c r="M38">
-        <v>0.3179764800000001</v>
+        <v>0.32680916</v>
       </c>
       <c r="N38">
-        <v>4.756023519999999</v>
+        <v>4.74719084</v>
       </c>
       <c r="O38">
-        <v>1.2841263504</v>
+        <v>1.2817415268</v>
       </c>
       <c r="P38">
-        <v>3.471897169599999</v>
+        <v>3.4654493132</v>
       </c>
       <c r="Q38">
-        <v>4.357897169599999</v>
+        <v>4.3514493132</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1405013802363092</v>
+        <v>0.1417168581423037</v>
       </c>
       <c r="T38">
-        <v>1.134498133008763</v>
+        <v>1.149059245123742</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4423,7 +4423,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>15.95715507008568</v>
+        <v>15.52588060873202</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4431,22 +4431,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1028676506296513</v>
+        <v>0.1025955779080648</v>
       </c>
       <c r="C39">
-        <v>14.1568269173508</v>
+        <v>14.07995689461158</v>
       </c>
       <c r="D39">
-        <v>20.6100269173508</v>
+        <v>20.70875689461158</v>
       </c>
       <c r="E39">
-        <v>-4.8028</v>
+        <v>-4.6272</v>
       </c>
       <c r="F39">
-        <v>6.497200000000001</v>
+        <v>6.672800000000001</v>
       </c>
       <c r="G39">
         <v>0.044</v>
@@ -4467,28 +4467,28 @@
         <v>5.074</v>
       </c>
       <c r="M39">
-        <v>0.32680916</v>
+        <v>0.33564184</v>
       </c>
       <c r="N39">
-        <v>4.74719084</v>
+        <v>4.73835816</v>
       </c>
       <c r="O39">
-        <v>1.2817415268</v>
+        <v>1.2793567032</v>
       </c>
       <c r="P39">
-        <v>3.4654493132</v>
+        <v>3.4590014568</v>
       </c>
       <c r="Q39">
-        <v>4.3514493132</v>
+        <v>4.345001456799999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1417168581423037</v>
+        <v>0.1429715450130077</v>
       </c>
       <c r="T39">
-        <v>1.149059245123742</v>
+        <v>1.164090070532753</v>
       </c>
       <c r="U39">
         <v>0.0503</v>
@@ -4505,7 +4505,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>15.52588060873202</v>
+        <v>15.11730480323907</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4513,22 +4513,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1025955779080648</v>
+        <v>0.1023235051864782</v>
       </c>
       <c r="C40">
-        <v>14.07995689461158</v>
+        <v>14.00403733428712</v>
       </c>
       <c r="D40">
-        <v>20.70875689461158</v>
+        <v>20.80843733428712</v>
       </c>
       <c r="E40">
-        <v>-4.6272</v>
+        <v>-4.4516</v>
       </c>
       <c r="F40">
-        <v>6.672800000000001</v>
+        <v>6.848400000000001</v>
       </c>
       <c r="G40">
         <v>0.044</v>
@@ -4549,28 +4549,28 @@
         <v>5.074</v>
       </c>
       <c r="M40">
-        <v>0.33564184</v>
+        <v>0.34447452</v>
       </c>
       <c r="N40">
-        <v>4.73835816</v>
+        <v>4.72952548</v>
       </c>
       <c r="O40">
-        <v>1.2793567032</v>
+        <v>1.2769718796</v>
       </c>
       <c r="P40">
-        <v>3.4590014568</v>
+        <v>3.452553600399999</v>
       </c>
       <c r="Q40">
-        <v>4.345001456799999</v>
+        <v>4.338553600399999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1429715450130077</v>
+        <v>0.144267369158161</v>
       </c>
       <c r="T40">
-        <v>1.164090070532753</v>
+        <v>1.1796137098896</v>
       </c>
       <c r="U40">
         <v>0.0503</v>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>15.11730480323907</v>
+        <v>14.72968160315602</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4595,22 +4595,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1023235051864782</v>
+        <v>0.1020514324648917</v>
       </c>
       <c r="C41">
-        <v>14.00403733428712</v>
+        <v>13.92908202775402</v>
       </c>
       <c r="D41">
-        <v>20.80843733428712</v>
+        <v>20.90908202775402</v>
       </c>
       <c r="E41">
-        <v>-4.4516</v>
+        <v>-4.276</v>
       </c>
       <c r="F41">
-        <v>6.848400000000001</v>
+        <v>7.024000000000001</v>
       </c>
       <c r="G41">
         <v>0.044</v>
@@ -4631,28 +4631,28 @@
         <v>5.074</v>
       </c>
       <c r="M41">
-        <v>0.34447452</v>
+        <v>0.3533072</v>
       </c>
       <c r="N41">
-        <v>4.72952548</v>
+        <v>4.7206928</v>
       </c>
       <c r="O41">
-        <v>1.2769718796</v>
+        <v>1.274587056</v>
       </c>
       <c r="P41">
-        <v>3.452553600399999</v>
+        <v>3.446105744</v>
       </c>
       <c r="Q41">
-        <v>4.338553600399999</v>
+        <v>4.332105744</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.144267369158161</v>
+        <v>0.1456063874414861</v>
       </c>
       <c r="T41">
-        <v>1.1796137098896</v>
+        <v>1.195654803891675</v>
       </c>
       <c r="U41">
         <v>0.0503</v>
@@ -4669,7 +4669,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>14.72968160315602</v>
+        <v>14.36143956307712</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4677,22 +4677,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1020514324648917</v>
+        <v>0.1017793597433051</v>
       </c>
       <c r="C42">
-        <v>13.92908202775402</v>
+        <v>13.85510503450604</v>
       </c>
       <c r="D42">
-        <v>20.90908202775402</v>
+        <v>21.01070503450604</v>
       </c>
       <c r="E42">
-        <v>-4.276</v>
+        <v>-4.1004</v>
       </c>
       <c r="F42">
-        <v>7.024000000000001</v>
+        <v>7.199600000000001</v>
       </c>
       <c r="G42">
         <v>0.044</v>
@@ -4713,28 +4713,28 @@
         <v>5.074</v>
       </c>
       <c r="M42">
-        <v>0.3533072</v>
+        <v>0.36213988</v>
       </c>
       <c r="N42">
-        <v>4.7206928</v>
+        <v>4.71186012</v>
       </c>
       <c r="O42">
-        <v>1.274587056</v>
+        <v>1.2722022324</v>
       </c>
       <c r="P42">
-        <v>3.446105744</v>
+        <v>3.4396578876</v>
       </c>
       <c r="Q42">
-        <v>4.332105744</v>
+        <v>4.3256578876</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1456063874414861</v>
+        <v>0.1469907961750934</v>
       </c>
       <c r="T42">
-        <v>1.195654803891675</v>
+        <v>1.212239663792126</v>
       </c>
       <c r="U42">
         <v>0.0503</v>
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>14.36143956307712</v>
+        <v>14.01116054934353</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1017793597433051</v>
+        <v>0.1015072870217186</v>
       </c>
       <c r="C43">
-        <v>13.85510503450604</v>
+        <v>13.78212068870154</v>
       </c>
       <c r="D43">
-        <v>21.01070503450604</v>
+        <v>21.11332068870154</v>
       </c>
       <c r="E43">
-        <v>-4.1004</v>
+        <v>-3.924799999999999</v>
       </c>
       <c r="F43">
-        <v>7.199600000000001</v>
+        <v>7.375200000000001</v>
       </c>
       <c r="G43">
         <v>0.044</v>
@@ -4795,28 +4795,28 @@
         <v>5.074</v>
       </c>
       <c r="M43">
-        <v>0.36213988</v>
+        <v>0.3709725600000001</v>
       </c>
       <c r="N43">
-        <v>4.71186012</v>
+        <v>4.70302744</v>
       </c>
       <c r="O43">
-        <v>1.2722022324</v>
+        <v>1.2698174088</v>
       </c>
       <c r="P43">
-        <v>3.4396578876</v>
+        <v>3.4332100312</v>
       </c>
       <c r="Q43">
-        <v>4.3256578876</v>
+        <v>4.3192100312</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1469907961750934</v>
+        <v>0.1484229431408941</v>
       </c>
       <c r="T43">
-        <v>1.212239663792126</v>
+        <v>1.229396415413282</v>
       </c>
       <c r="U43">
         <v>0.0503</v>
@@ -4833,7 +4833,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>14.01116054934353</v>
+        <v>13.67756148864487</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4841,22 +4841,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1015072870217186</v>
+        <v>0.101235214300132</v>
       </c>
       <c r="C44">
-        <v>13.78212068870154</v>
+        <v>13.71014360590366</v>
       </c>
       <c r="D44">
-        <v>21.11332068870154</v>
+        <v>21.21694360590366</v>
       </c>
       <c r="E44">
-        <v>-3.9248</v>
+        <v>-3.7492</v>
       </c>
       <c r="F44">
-        <v>7.3752</v>
+        <v>7.550800000000001</v>
       </c>
       <c r="G44">
         <v>0.044</v>
@@ -4877,28 +4877,28 @@
         <v>5.074</v>
       </c>
       <c r="M44">
-        <v>0.37097256</v>
+        <v>0.37980524</v>
       </c>
       <c r="N44">
-        <v>4.70302744</v>
+        <v>4.69419476</v>
       </c>
       <c r="O44">
-        <v>1.2698174088</v>
+        <v>1.2674325852</v>
       </c>
       <c r="P44">
-        <v>3.4332100312</v>
+        <v>3.4267621748</v>
       </c>
       <c r="Q44">
-        <v>4.3192100312</v>
+        <v>4.3127621748</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.148422943140894</v>
+        <v>0.1499053408774246</v>
       </c>
       <c r="T44">
-        <v>1.229396415413282</v>
+        <v>1.247155158319391</v>
       </c>
       <c r="U44">
         <v>0.0503</v>
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>13.67756148864487</v>
+        <v>13.35947866332755</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4923,22 +4923,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.101235214300132</v>
+        <v>0.1009631415785454</v>
       </c>
       <c r="C45">
-        <v>13.71014360590366</v>
+        <v>13.63918869001998</v>
       </c>
       <c r="D45">
-        <v>21.21694360590366</v>
+        <v>21.32158869001998</v>
       </c>
       <c r="E45">
-        <v>-3.7492</v>
+        <v>-3.5736</v>
       </c>
       <c r="F45">
-        <v>7.550800000000001</v>
+        <v>7.726400000000001</v>
       </c>
       <c r="G45">
         <v>0.044</v>
@@ -4959,28 +4959,28 @@
         <v>5.074</v>
       </c>
       <c r="M45">
-        <v>0.37980524</v>
+        <v>0.38863792</v>
       </c>
       <c r="N45">
-        <v>4.69419476</v>
+        <v>4.68536208</v>
       </c>
       <c r="O45">
-        <v>1.2674325852</v>
+        <v>1.2650477616</v>
       </c>
       <c r="P45">
-        <v>3.4267621748</v>
+        <v>3.4203143184</v>
       </c>
       <c r="Q45">
-        <v>4.3127621748</v>
+        <v>4.3063143184</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1499053408774246</v>
+        <v>0.1514406813902597</v>
       </c>
       <c r="T45">
-        <v>1.247155158319391</v>
+        <v>1.265548142043575</v>
       </c>
       <c r="U45">
         <v>0.0503</v>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>13.35947866332755</v>
+        <v>13.05585414825192</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5005,22 +5005,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1009631415785454</v>
+        <v>0.1011838188569589</v>
       </c>
       <c r="C46">
-        <v>13.63918869001998</v>
+        <v>13.37863264580575</v>
       </c>
       <c r="D46">
-        <v>21.32158869001998</v>
+        <v>21.23663264580575</v>
       </c>
       <c r="E46">
-        <v>-3.5736</v>
+        <v>-3.398</v>
       </c>
       <c r="F46">
-        <v>7.726400000000001</v>
+        <v>7.902000000000001</v>
       </c>
       <c r="G46">
         <v>0.044</v>
@@ -5041,45 +5041,45 @@
         <v>5.074</v>
       </c>
       <c r="M46">
-        <v>0.38863792</v>
+        <v>0.4093236000000001</v>
       </c>
       <c r="N46">
-        <v>4.68536208</v>
+        <v>4.664676399999999</v>
       </c>
       <c r="O46">
-        <v>1.2650477616</v>
+        <v>1.259462628</v>
       </c>
       <c r="P46">
-        <v>3.4203143184</v>
+        <v>3.405213772</v>
       </c>
       <c r="Q46">
-        <v>4.3063143184</v>
+        <v>4.291213772</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1514406813902597</v>
+        <v>0.153031852467198</v>
       </c>
       <c r="T46">
-        <v>1.265548142043575</v>
+        <v>1.284609961539548</v>
       </c>
       <c r="U46">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V46">
         <v>0.27</v>
       </c>
       <c r="W46">
-        <v>0.03671899999999999</v>
+        <v>0.037814</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y46">
-        <v>13.05585414825192</v>
+        <v>12.39606023205112</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5087,22 +5087,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1011838188569589</v>
+        <v>0.1009226961353723</v>
       </c>
       <c r="C47">
-        <v>13.37863264580575</v>
+        <v>13.30363308269636</v>
       </c>
       <c r="D47">
-        <v>21.23663264580575</v>
+        <v>21.33723308269636</v>
       </c>
       <c r="E47">
-        <v>-3.398</v>
+        <v>-3.222399999999999</v>
       </c>
       <c r="F47">
-        <v>7.902000000000001</v>
+        <v>8.077600000000002</v>
       </c>
       <c r="G47">
         <v>0.044</v>
@@ -5123,28 +5123,28 @@
         <v>5.074</v>
       </c>
       <c r="M47">
-        <v>0.4093236000000001</v>
+        <v>0.4184196800000001</v>
       </c>
       <c r="N47">
-        <v>4.664676399999999</v>
+        <v>4.655580319999999</v>
       </c>
       <c r="O47">
-        <v>1.259462628</v>
+        <v>1.2570066864</v>
       </c>
       <c r="P47">
-        <v>3.405213772</v>
+        <v>3.398573633599999</v>
       </c>
       <c r="Q47">
-        <v>4.291213772</v>
+        <v>4.284573633599999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.153031852467198</v>
+        <v>0.1546819558062451</v>
       </c>
       <c r="T47">
-        <v>1.284609961539548</v>
+        <v>1.304377774350186</v>
       </c>
       <c r="U47">
         <v>0.0518</v>
@@ -5161,7 +5161,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>12.39606023205112</v>
+        <v>12.12658066178913</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5169,22 +5169,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1009226961353723</v>
+        <v>0.1006615734137858</v>
       </c>
       <c r="C48">
-        <v>13.30363308269636</v>
+        <v>13.22959116838335</v>
       </c>
       <c r="D48">
-        <v>21.33723308269636</v>
+        <v>21.43879116838335</v>
       </c>
       <c r="E48">
-        <v>-3.222399999999999</v>
+        <v>-3.046799999999999</v>
       </c>
       <c r="F48">
-        <v>8.077600000000002</v>
+        <v>8.253200000000001</v>
       </c>
       <c r="G48">
         <v>0.044</v>
@@ -5205,28 +5205,28 @@
         <v>5.074</v>
       </c>
       <c r="M48">
-        <v>0.4184196800000001</v>
+        <v>0.4275157600000001</v>
       </c>
       <c r="N48">
-        <v>4.655580319999999</v>
+        <v>4.646484239999999</v>
       </c>
       <c r="O48">
-        <v>1.2570066864</v>
+        <v>1.2545507448</v>
       </c>
       <c r="P48">
-        <v>3.398573633599999</v>
+        <v>3.3919334952</v>
       </c>
       <c r="Q48">
-        <v>4.284573633599999</v>
+        <v>4.277933495199999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1546819558062451</v>
+        <v>0.1563943271958222</v>
       </c>
       <c r="T48">
-        <v>1.304377774350186</v>
+        <v>1.324891542361226</v>
       </c>
       <c r="U48">
         <v>0.0518</v>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>12.12658066178913</v>
+        <v>11.86856830728298</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5251,22 +5251,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1006615734137858</v>
+        <v>0.1004004506921992</v>
       </c>
       <c r="C49">
-        <v>13.22959116838335</v>
+        <v>13.15652064252583</v>
       </c>
       <c r="D49">
-        <v>21.43879116838335</v>
+        <v>21.54132064252583</v>
       </c>
       <c r="E49">
-        <v>-3.046799999999999</v>
+        <v>-2.871199999999998</v>
       </c>
       <c r="F49">
-        <v>8.253200000000001</v>
+        <v>8.428800000000003</v>
       </c>
       <c r="G49">
         <v>0.044</v>
@@ -5287,28 +5287,28 @@
         <v>5.074</v>
       </c>
       <c r="M49">
-        <v>0.4275157600000001</v>
+        <v>0.4366118400000001</v>
       </c>
       <c r="N49">
-        <v>4.646484239999999</v>
+        <v>4.63738816</v>
       </c>
       <c r="O49">
-        <v>1.2545507448</v>
+        <v>1.2520948032</v>
       </c>
       <c r="P49">
-        <v>3.3919334952</v>
+        <v>3.3852933568</v>
       </c>
       <c r="Q49">
-        <v>4.277933495199999</v>
+        <v>4.271293356799999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1563943271958222</v>
+        <v>0.1581725590234601</v>
       </c>
       <c r="T49">
-        <v>1.324891542361226</v>
+        <v>1.346194301449613</v>
       </c>
       <c r="U49">
         <v>0.0518</v>
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>11.86856830728298</v>
+        <v>11.62130646754792</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5333,22 +5333,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1004004506921992</v>
+        <v>0.1001393279706126</v>
       </c>
       <c r="C50">
-        <v>13.15652064252584</v>
+        <v>13.0844355088817</v>
       </c>
       <c r="D50">
-        <v>21.54132064252584</v>
+        <v>21.6448355088817</v>
       </c>
       <c r="E50">
-        <v>-2.8712</v>
+        <v>-2.695599999999999</v>
       </c>
       <c r="F50">
-        <v>8.428800000000001</v>
+        <v>8.604400000000002</v>
       </c>
       <c r="G50">
         <v>0.044</v>
@@ -5369,28 +5369,28 @@
         <v>5.074</v>
       </c>
       <c r="M50">
-        <v>0.43661184</v>
+        <v>0.4457079200000001</v>
       </c>
       <c r="N50">
-        <v>4.63738816</v>
+        <v>4.62829208</v>
       </c>
       <c r="O50">
-        <v>1.2520948032</v>
+        <v>1.2496388616</v>
       </c>
       <c r="P50">
-        <v>3.3852933568</v>
+        <v>3.378653218399999</v>
       </c>
       <c r="Q50">
-        <v>4.271293356799999</v>
+        <v>4.264653218399999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1581725590234601</v>
+        <v>0.1600205254325738</v>
       </c>
       <c r="T50">
-        <v>1.346194301449613</v>
+        <v>1.368332462855192</v>
       </c>
       <c r="U50">
         <v>0.0518</v>
@@ -5407,7 +5407,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>11.62130646754792</v>
+        <v>11.38413694780205</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5415,22 +5415,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1001393279706126</v>
+        <v>0.0998782052490261</v>
       </c>
       <c r="C51">
-        <v>13.0844355088817</v>
+        <v>13.01335004168369</v>
       </c>
       <c r="D51">
-        <v>21.6448355088817</v>
+        <v>21.74935004168369</v>
       </c>
       <c r="E51">
-        <v>-2.695599999999999</v>
+        <v>-2.52</v>
       </c>
       <c r="F51">
-        <v>8.604400000000002</v>
+        <v>8.780000000000001</v>
       </c>
       <c r="G51">
         <v>0.044</v>
@@ -5451,28 +5451,28 @@
         <v>5.074</v>
       </c>
       <c r="M51">
-        <v>0.4457079200000001</v>
+        <v>0.454804</v>
       </c>
       <c r="N51">
-        <v>4.62829208</v>
+        <v>4.619196</v>
       </c>
       <c r="O51">
-        <v>1.2496388616</v>
+        <v>1.24718292</v>
       </c>
       <c r="P51">
-        <v>3.378653218399999</v>
+        <v>3.372013079999999</v>
       </c>
       <c r="Q51">
-        <v>4.264653218399999</v>
+        <v>4.25801308</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1600205254325738</v>
+        <v>0.1619424104980522</v>
       </c>
       <c r="T51">
-        <v>1.368332462855192</v>
+        <v>1.391356150716994</v>
       </c>
       <c r="U51">
         <v>0.0518</v>
@@ -5489,7 +5489,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>11.38413694780205</v>
+        <v>11.15645420884601</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5497,22 +5497,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.0998782052490261</v>
+        <v>0.09961708252743956</v>
       </c>
       <c r="C52">
-        <v>13.01335004168369</v>
+        <v>12.94327879220129</v>
       </c>
       <c r="D52">
-        <v>21.74935004168369</v>
+        <v>21.85487879220129</v>
       </c>
       <c r="E52">
-        <v>-2.52</v>
+        <v>-2.3444</v>
       </c>
       <c r="F52">
-        <v>8.780000000000001</v>
+        <v>8.9556</v>
       </c>
       <c r="G52">
         <v>0.044</v>
@@ -5533,28 +5533,28 @@
         <v>5.074</v>
       </c>
       <c r="M52">
-        <v>0.454804</v>
+        <v>0.46390008</v>
       </c>
       <c r="N52">
-        <v>4.619196</v>
+        <v>4.61009992</v>
       </c>
       <c r="O52">
-        <v>1.24718292</v>
+        <v>1.2447269784</v>
       </c>
       <c r="P52">
-        <v>3.372013079999999</v>
+        <v>3.3653729416</v>
       </c>
       <c r="Q52">
-        <v>4.25801308</v>
+        <v>4.2513729416</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1619424104980522</v>
+        <v>0.1639427398519175</v>
       </c>
       <c r="T52">
-        <v>1.391356150716994</v>
+        <v>1.415319580940503</v>
       </c>
       <c r="U52">
         <v>0.0518</v>
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>11.15645420884601</v>
+        <v>10.93770020475099</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5579,22 +5579,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09961708252743956</v>
+        <v>0.099355959805853</v>
       </c>
       <c r="C53">
-        <v>12.94327879220129</v>
+        <v>12.87423659549436</v>
       </c>
       <c r="D53">
-        <v>21.85487879220129</v>
+        <v>21.96143659549437</v>
       </c>
       <c r="E53">
-        <v>-2.3444</v>
+        <v>-2.168799999999999</v>
       </c>
       <c r="F53">
-        <v>8.9556</v>
+        <v>9.131200000000002</v>
       </c>
       <c r="G53">
         <v>0.044</v>
@@ -5615,28 +5615,28 @@
         <v>5.074</v>
       </c>
       <c r="M53">
-        <v>0.46390008</v>
+        <v>0.4729961600000001</v>
       </c>
       <c r="N53">
-        <v>4.61009992</v>
+        <v>4.60100384</v>
       </c>
       <c r="O53">
-        <v>1.2447269784</v>
+        <v>1.2422710368</v>
       </c>
       <c r="P53">
-        <v>3.3653729416</v>
+        <v>3.3587328032</v>
       </c>
       <c r="Q53">
-        <v>4.2513729416</v>
+        <v>4.2447328032</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1639427398519175</v>
+        <v>0.1660264162621937</v>
       </c>
       <c r="T53">
-        <v>1.415319580940503</v>
+        <v>1.440281487423324</v>
       </c>
       <c r="U53">
         <v>0.0518</v>
@@ -5653,7 +5653,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>10.93770020475099</v>
+        <v>10.72735981619808</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5661,22 +5661,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.099355959805853</v>
+        <v>0.09909483708426645</v>
       </c>
       <c r="C54">
-        <v>12.87423659549436</v>
+        <v>12.8062385773655</v>
       </c>
       <c r="D54">
-        <v>21.96143659549437</v>
+        <v>22.0690385773655</v>
       </c>
       <c r="E54">
-        <v>-2.168799999999999</v>
+        <v>-1.9932</v>
       </c>
       <c r="F54">
-        <v>9.131200000000002</v>
+        <v>9.306800000000001</v>
       </c>
       <c r="G54">
         <v>0.044</v>
@@ -5697,28 +5697,28 @@
         <v>5.074</v>
       </c>
       <c r="M54">
-        <v>0.4729961600000001</v>
+        <v>0.4820922400000001</v>
       </c>
       <c r="N54">
-        <v>4.60100384</v>
+        <v>4.59190776</v>
       </c>
       <c r="O54">
-        <v>1.2422710368</v>
+        <v>1.2398150952</v>
       </c>
       <c r="P54">
-        <v>3.3587328032</v>
+        <v>3.3520926648</v>
       </c>
       <c r="Q54">
-        <v>4.2447328032</v>
+        <v>4.2380926648</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1660264162621937</v>
+        <v>0.1681987597537584</v>
       </c>
       <c r="T54">
-        <v>1.440281487423324</v>
+        <v>1.466305602692649</v>
       </c>
       <c r="U54">
         <v>0.0518</v>
@@ -5735,7 +5735,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>10.72735981619808</v>
+        <v>10.52495680079812</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5743,22 +5743,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09909483708426645</v>
+        <v>0.09883371436267989</v>
       </c>
       <c r="C55">
-        <v>12.8062385773655</v>
+        <v>12.73930016151762</v>
       </c>
       <c r="D55">
-        <v>22.0690385773655</v>
+        <v>22.17770016151762</v>
       </c>
       <c r="E55">
-        <v>-1.9932</v>
+        <v>-1.817599999999999</v>
       </c>
       <c r="F55">
-        <v>9.306800000000001</v>
+        <v>9.482400000000002</v>
       </c>
       <c r="G55">
         <v>0.044</v>
@@ -5779,28 +5779,28 @@
         <v>5.074</v>
       </c>
       <c r="M55">
-        <v>0.4820922400000001</v>
+        <v>0.4911883200000001</v>
       </c>
       <c r="N55">
-        <v>4.59190776</v>
+        <v>4.58281168</v>
       </c>
       <c r="O55">
-        <v>1.2398150952</v>
+        <v>1.2373591536</v>
       </c>
       <c r="P55">
-        <v>3.3520926648</v>
+        <v>3.3454525264</v>
       </c>
       <c r="Q55">
-        <v>4.2380926648</v>
+        <v>4.2314525264</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1681987597537584</v>
+        <v>0.1704655529623476</v>
       </c>
       <c r="T55">
-        <v>1.466305602692649</v>
+        <v>1.493461201234552</v>
       </c>
       <c r="U55">
         <v>0.0518</v>
@@ -5817,7 +5817,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>10.52495680079812</v>
+        <v>10.33005019337593</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09883371436267989</v>
+        <v>0.09857259164109333</v>
       </c>
       <c r="C56">
-        <v>12.73930016151762</v>
+        <v>12.67343707692423</v>
       </c>
       <c r="D56">
-        <v>22.17770016151762</v>
+        <v>22.28743707692423</v>
       </c>
       <c r="E56">
-        <v>-1.817599999999999</v>
+        <v>-1.641999999999999</v>
       </c>
       <c r="F56">
-        <v>9.482400000000002</v>
+        <v>9.658000000000001</v>
       </c>
       <c r="G56">
         <v>0.044</v>
@@ -5861,28 +5861,28 @@
         <v>5.074</v>
       </c>
       <c r="M56">
-        <v>0.4911883200000001</v>
+        <v>0.5002844000000001</v>
       </c>
       <c r="N56">
-        <v>4.58281168</v>
+        <v>4.5737156</v>
       </c>
       <c r="O56">
-        <v>1.2373591536</v>
+        <v>1.234903212</v>
       </c>
       <c r="P56">
-        <v>3.3454525264</v>
+        <v>3.338812388</v>
       </c>
       <c r="Q56">
-        <v>4.2314525264</v>
+        <v>4.224812388</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1704655529623476</v>
+        <v>0.172833092535763</v>
       </c>
       <c r="T56">
-        <v>1.493461201234552</v>
+        <v>1.521823715267207</v>
       </c>
       <c r="U56">
         <v>0.0518</v>
@@ -5899,7 +5899,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>10.33005019337593</v>
+        <v>10.14223109895092</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5907,22 +5907,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09857259164109333</v>
+        <v>0.09831146891950678</v>
       </c>
       <c r="C57">
-        <v>12.67343707692423</v>
+        <v>12.60866536541939</v>
       </c>
       <c r="D57">
-        <v>22.28743707692423</v>
+        <v>22.39826536541939</v>
       </c>
       <c r="E57">
-        <v>-1.641999999999999</v>
+        <v>-1.466399999999998</v>
       </c>
       <c r="F57">
-        <v>9.658000000000001</v>
+        <v>9.833600000000002</v>
       </c>
       <c r="G57">
         <v>0.044</v>
@@ -5943,28 +5943,28 @@
         <v>5.074</v>
       </c>
       <c r="M57">
-        <v>0.5002844000000001</v>
+        <v>0.5093804800000001</v>
       </c>
       <c r="N57">
-        <v>4.5737156</v>
+        <v>4.56461952</v>
       </c>
       <c r="O57">
-        <v>1.234903212</v>
+        <v>1.2324472704</v>
       </c>
       <c r="P57">
-        <v>3.338812388</v>
+        <v>3.3321722496</v>
       </c>
       <c r="Q57">
-        <v>4.224812388</v>
+        <v>4.2181722496</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.172833092535763</v>
+        <v>0.1753082475443336</v>
       </c>
       <c r="T57">
-        <v>1.521823715267207</v>
+        <v>1.551475434483165</v>
       </c>
       <c r="U57">
         <v>0.0518</v>
@@ -5981,7 +5981,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>10.14223109895092</v>
+        <v>9.96111982932679</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5989,22 +5989,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09831146891950678</v>
+        <v>0.09875771619792023</v>
       </c>
       <c r="C58">
-        <v>12.60866536541939</v>
+        <v>12.24432677021363</v>
       </c>
       <c r="D58">
-        <v>22.39826536541939</v>
+        <v>22.20952677021363</v>
       </c>
       <c r="E58">
-        <v>-1.466399999999998</v>
+        <v>-1.290799999999999</v>
       </c>
       <c r="F58">
-        <v>9.833600000000002</v>
+        <v>10.0092</v>
       </c>
       <c r="G58">
         <v>0.044</v>
@@ -6025,45 +6025,45 @@
         <v>5.074</v>
       </c>
       <c r="M58">
-        <v>0.5093804800000001</v>
+        <v>0.5354922000000001</v>
       </c>
       <c r="N58">
-        <v>4.56461952</v>
+        <v>4.5385078</v>
       </c>
       <c r="O58">
-        <v>1.2324472704</v>
+        <v>1.225397106</v>
       </c>
       <c r="P58">
-        <v>3.3321722496</v>
+        <v>3.313110694</v>
       </c>
       <c r="Q58">
-        <v>4.2181722496</v>
+        <v>4.199110694</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1753082475443336</v>
+        <v>0.177898526041675</v>
       </c>
       <c r="T58">
-        <v>1.551475434483165</v>
+        <v>1.582506303430097</v>
       </c>
       <c r="U58">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V58">
         <v>0.27</v>
       </c>
       <c r="W58">
-        <v>0.037814</v>
+        <v>0.039055</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y58">
-        <v>9.96111982932679</v>
+        <v>9.475394786329286</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6071,22 +6071,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09875771619792023</v>
+        <v>0.09850900347633368</v>
       </c>
       <c r="C59">
-        <v>12.24432677021363</v>
+        <v>12.17352465072467</v>
       </c>
       <c r="D59">
-        <v>22.20952677021363</v>
+        <v>22.31432465072468</v>
       </c>
       <c r="E59">
-        <v>-1.290799999999999</v>
+        <v>-1.115199999999998</v>
       </c>
       <c r="F59">
-        <v>10.0092</v>
+        <v>10.1848</v>
       </c>
       <c r="G59">
         <v>0.044</v>
@@ -6107,28 +6107,28 @@
         <v>5.074</v>
       </c>
       <c r="M59">
-        <v>0.5354922000000001</v>
+        <v>0.5448868000000001</v>
       </c>
       <c r="N59">
-        <v>4.5385078</v>
+        <v>4.529113199999999</v>
       </c>
       <c r="O59">
-        <v>1.225397106</v>
+        <v>1.222860564</v>
       </c>
       <c r="P59">
-        <v>3.313110694</v>
+        <v>3.306252636</v>
       </c>
       <c r="Q59">
-        <v>4.199110694</v>
+        <v>4.192252635999999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.177898526041675</v>
+        <v>0.1806121511341278</v>
       </c>
       <c r="T59">
-        <v>1.582506303430097</v>
+        <v>1.615014832803074</v>
       </c>
       <c r="U59">
         <v>0.0535</v>
@@ -6145,7 +6145,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>9.475394786329286</v>
+        <v>9.312025910702918</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6153,22 +6153,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09850900347633366</v>
+        <v>0.09826029075474713</v>
       </c>
       <c r="C60">
-        <v>12.17352465072468</v>
+        <v>12.1037162186783</v>
       </c>
       <c r="D60">
-        <v>22.31432465072468</v>
+        <v>22.4201162186783</v>
       </c>
       <c r="E60">
-        <v>-1.1152</v>
+        <v>-0.9396000000000004</v>
       </c>
       <c r="F60">
-        <v>10.1848</v>
+        <v>10.3604</v>
       </c>
       <c r="G60">
         <v>0.044</v>
@@ -6189,28 +6189,28 @@
         <v>5.074</v>
       </c>
       <c r="M60">
-        <v>0.5448868</v>
+        <v>0.5542814</v>
       </c>
       <c r="N60">
-        <v>4.529113199999999</v>
+        <v>4.5197186</v>
       </c>
       <c r="O60">
-        <v>1.222860564</v>
+        <v>1.220324022</v>
       </c>
       <c r="P60">
-        <v>3.306252636</v>
+        <v>3.299394578</v>
       </c>
       <c r="Q60">
-        <v>4.192252635999999</v>
+        <v>4.185394578</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1806121511341278</v>
+        <v>0.18345814818231</v>
       </c>
       <c r="T60">
-        <v>1.615014832803073</v>
+        <v>1.649109144096683</v>
       </c>
       <c r="U60">
         <v>0.0535</v>
@@ -6227,7 +6227,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>9.31202591070292</v>
+        <v>9.154194963063887</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6235,22 +6235,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09826029075474713</v>
+        <v>0.09801157803316056</v>
       </c>
       <c r="C61">
-        <v>12.1037162186783</v>
+        <v>12.03491567452874</v>
       </c>
       <c r="D61">
-        <v>22.4201162186783</v>
+        <v>22.52691567452874</v>
       </c>
       <c r="E61">
-        <v>-0.9396000000000004</v>
+        <v>-0.7639999999999993</v>
       </c>
       <c r="F61">
-        <v>10.3604</v>
+        <v>10.536</v>
       </c>
       <c r="G61">
         <v>0.044</v>
@@ -6271,28 +6271,28 @@
         <v>5.074</v>
       </c>
       <c r="M61">
-        <v>0.5542814</v>
+        <v>0.5636760000000001</v>
       </c>
       <c r="N61">
-        <v>4.5197186</v>
+        <v>4.510324</v>
       </c>
       <c r="O61">
-        <v>1.220324022</v>
+        <v>1.21778748</v>
       </c>
       <c r="P61">
-        <v>3.299394578</v>
+        <v>3.29253652</v>
       </c>
       <c r="Q61">
-        <v>4.185394578</v>
+        <v>4.17853652</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.18345814818231</v>
+        <v>0.1864464450829014</v>
       </c>
       <c r="T61">
-        <v>1.649109144096683</v>
+        <v>1.684908170954973</v>
       </c>
       <c r="U61">
         <v>0.0535</v>
@@ -6309,7 +6309,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>9.154194963063887</v>
+        <v>9.001625047012821</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6317,22 +6317,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09801157803316056</v>
+        <v>0.09776286531157401</v>
       </c>
       <c r="C62">
-        <v>12.03491567452874</v>
+        <v>11.96713749060391</v>
       </c>
       <c r="D62">
-        <v>22.52691567452874</v>
+        <v>22.63473749060391</v>
       </c>
       <c r="E62">
-        <v>-0.7639999999999993</v>
+        <v>-0.5884</v>
       </c>
       <c r="F62">
-        <v>10.536</v>
+        <v>10.7116</v>
       </c>
       <c r="G62">
         <v>0.044</v>
@@ -6353,28 +6353,28 @@
         <v>5.074</v>
       </c>
       <c r="M62">
-        <v>0.5636760000000001</v>
+        <v>0.5730706</v>
       </c>
       <c r="N62">
-        <v>4.510324</v>
+        <v>4.5009294</v>
       </c>
       <c r="O62">
-        <v>1.21778748</v>
+        <v>1.215250938</v>
       </c>
       <c r="P62">
-        <v>3.29253652</v>
+        <v>3.285678461999999</v>
       </c>
       <c r="Q62">
-        <v>4.17853652</v>
+        <v>4.171678461999999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1864464450829014</v>
+        <v>0.1895879879783949</v>
       </c>
       <c r="T62">
-        <v>1.684908170954973</v>
+        <v>1.722543045344457</v>
       </c>
       <c r="U62">
         <v>0.0535</v>
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>9.001625047012821</v>
+        <v>8.854057423291302</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6399,22 +6399,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09776286531157401</v>
+        <v>0.09751415258998745</v>
       </c>
       <c r="C63">
-        <v>11.96713749060391</v>
+        <v>11.90039641764306</v>
       </c>
       <c r="D63">
-        <v>22.63473749060391</v>
+        <v>22.74359641764306</v>
       </c>
       <c r="E63">
-        <v>-0.5884</v>
+        <v>-0.4127999999999989</v>
       </c>
       <c r="F63">
-        <v>10.7116</v>
+        <v>10.8872</v>
       </c>
       <c r="G63">
         <v>0.044</v>
@@ -6435,28 +6435,28 @@
         <v>5.074</v>
       </c>
       <c r="M63">
-        <v>0.5730706</v>
+        <v>0.5824652000000001</v>
       </c>
       <c r="N63">
-        <v>4.5009294</v>
+        <v>4.4915348</v>
       </c>
       <c r="O63">
-        <v>1.215250938</v>
+        <v>1.212714396</v>
       </c>
       <c r="P63">
-        <v>3.285678461999999</v>
+        <v>3.278820404</v>
       </c>
       <c r="Q63">
-        <v>4.171678461999999</v>
+        <v>4.164820404</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1895879879783949</v>
+        <v>0.1928948752368091</v>
       </c>
       <c r="T63">
-        <v>1.722543045344457</v>
+        <v>1.762158702596546</v>
       </c>
       <c r="U63">
         <v>0.0535</v>
@@ -6473,7 +6473,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>8.854057423291302</v>
+        <v>8.711250045496278</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6481,22 +6481,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09751415258998745</v>
+        <v>0.09726543986840089</v>
       </c>
       <c r="C64">
-        <v>11.90039641764306</v>
+        <v>11.83470749152415</v>
       </c>
       <c r="D64">
-        <v>22.74359641764306</v>
+        <v>22.85350749152415</v>
       </c>
       <c r="E64">
-        <v>-0.4127999999999989</v>
+        <v>-0.2371999999999996</v>
       </c>
       <c r="F64">
-        <v>10.8872</v>
+        <v>11.0628</v>
       </c>
       <c r="G64">
         <v>0.044</v>
@@ -6517,28 +6517,28 @@
         <v>5.074</v>
       </c>
       <c r="M64">
-        <v>0.5824652000000001</v>
+        <v>0.5918598</v>
       </c>
       <c r="N64">
-        <v>4.4915348</v>
+        <v>4.4821402</v>
       </c>
       <c r="O64">
-        <v>1.212714396</v>
+        <v>1.210177854</v>
       </c>
       <c r="P64">
-        <v>3.278820404</v>
+        <v>3.271962346</v>
       </c>
       <c r="Q64">
-        <v>4.164820404</v>
+        <v>4.157962346</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1928948752368091</v>
+        <v>0.1963805131578402</v>
       </c>
       <c r="T64">
-        <v>1.762158702596546</v>
+        <v>1.803915746727127</v>
       </c>
       <c r="U64">
         <v>0.0535</v>
@@ -6555,7 +6555,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>8.711250045496278</v>
+        <v>8.572976235250307</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6563,22 +6563,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09726543986840089</v>
+        <v>0.09701672714681435</v>
       </c>
       <c r="C65">
-        <v>11.83470749152415</v>
+        <v>11.77008604018701</v>
       </c>
       <c r="D65">
-        <v>22.85350749152415</v>
+        <v>22.96448604018701</v>
       </c>
       <c r="E65">
-        <v>-0.2371999999999996</v>
+        <v>-0.06159999999999854</v>
       </c>
       <c r="F65">
-        <v>11.0628</v>
+        <v>11.2384</v>
       </c>
       <c r="G65">
         <v>0.044</v>
@@ -6599,28 +6599,28 @@
         <v>5.074</v>
       </c>
       <c r="M65">
-        <v>0.5918598</v>
+        <v>0.6012544000000001</v>
       </c>
       <c r="N65">
-        <v>4.4821402</v>
+        <v>4.4727456</v>
       </c>
       <c r="O65">
-        <v>1.210177854</v>
+        <v>1.207641312</v>
       </c>
       <c r="P65">
-        <v>3.271962346</v>
+        <v>3.265104288</v>
       </c>
       <c r="Q65">
-        <v>4.157962346</v>
+        <v>4.151104288</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1963805131578402</v>
+        <v>0.2000597976300399</v>
       </c>
       <c r="T65">
-        <v>1.803915746727127</v>
+        <v>1.847992626642739</v>
       </c>
       <c r="U65">
         <v>0.0535</v>
@@ -6637,7 +6637,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>8.572976235250307</v>
+        <v>8.43902348157452</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6645,22 +6645,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09701672714681435</v>
+        <v>0.09676801442522778</v>
       </c>
       <c r="C66">
-        <v>11.77008604018701</v>
+        <v>11.70654769075946</v>
       </c>
       <c r="D66">
-        <v>22.96448604018701</v>
+        <v>23.07654769075947</v>
       </c>
       <c r="E66">
-        <v>-0.06159999999999854</v>
+        <v>0.1140000000000008</v>
       </c>
       <c r="F66">
-        <v>11.2384</v>
+        <v>11.414</v>
       </c>
       <c r="G66">
         <v>0.044</v>
@@ -6681,28 +6681,28 @@
         <v>5.074</v>
       </c>
       <c r="M66">
-        <v>0.6012544000000001</v>
+        <v>0.6106490000000001</v>
       </c>
       <c r="N66">
-        <v>4.4727456</v>
+        <v>4.463350999999999</v>
       </c>
       <c r="O66">
-        <v>1.207641312</v>
+        <v>1.20510477</v>
       </c>
       <c r="P66">
-        <v>3.265104288</v>
+        <v>3.258246229999999</v>
       </c>
       <c r="Q66">
-        <v>4.151104288</v>
+        <v>4.144246229999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2000597976300399</v>
+        <v>0.2039493269292223</v>
       </c>
       <c r="T66">
-        <v>1.847992626642739</v>
+        <v>1.894588185410672</v>
       </c>
       <c r="U66">
         <v>0.0535</v>
@@ -6719,7 +6719,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>8.43902348157452</v>
+        <v>8.309192351088758</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6727,22 +6727,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09676801442522778</v>
+        <v>0.09651930170364122</v>
       </c>
       <c r="C67">
-        <v>11.70654769075946</v>
+        <v>11.64410837689286</v>
       </c>
       <c r="D67">
-        <v>23.07654769075947</v>
+        <v>23.18970837689287</v>
       </c>
       <c r="E67">
-        <v>0.1140000000000008</v>
+        <v>0.2896000000000019</v>
       </c>
       <c r="F67">
-        <v>11.414</v>
+        <v>11.5896</v>
       </c>
       <c r="G67">
         <v>0.044</v>
@@ -6763,28 +6763,28 @@
         <v>5.074</v>
       </c>
       <c r="M67">
-        <v>0.6106490000000001</v>
+        <v>0.6200436000000001</v>
       </c>
       <c r="N67">
-        <v>4.463350999999999</v>
+        <v>4.4539564</v>
       </c>
       <c r="O67">
-        <v>1.20510477</v>
+        <v>1.202568228</v>
       </c>
       <c r="P67">
-        <v>3.258246229999999</v>
+        <v>3.251388172</v>
       </c>
       <c r="Q67">
-        <v>4.144246229999999</v>
+        <v>4.137388172</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2039493269292223</v>
+        <v>0.208067652069533</v>
       </c>
       <c r="T67">
-        <v>1.894588185410672</v>
+        <v>1.943924659400248</v>
       </c>
       <c r="U67">
         <v>0.0535</v>
@@ -6801,7 +6801,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>8.309192351088758</v>
+        <v>8.183295497284384</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6809,22 +6809,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09651930170364122</v>
+        <v>0.09627058898205468</v>
       </c>
       <c r="C68">
-        <v>11.64410837689286</v>
+        <v>11.5827843463147</v>
       </c>
       <c r="D68">
-        <v>23.18970837689287</v>
+        <v>23.3039843463147</v>
       </c>
       <c r="E68">
-        <v>0.2896000000000019</v>
+        <v>0.4652000000000012</v>
       </c>
       <c r="F68">
-        <v>11.5896</v>
+        <v>11.7652</v>
       </c>
       <c r="G68">
         <v>0.044</v>
@@ -6845,28 +6845,28 @@
         <v>5.074</v>
       </c>
       <c r="M68">
-        <v>0.6200436000000001</v>
+        <v>0.6294382000000001</v>
       </c>
       <c r="N68">
-        <v>4.4539564</v>
+        <v>4.4445618</v>
       </c>
       <c r="O68">
-        <v>1.202568228</v>
+        <v>1.200031686</v>
       </c>
       <c r="P68">
-        <v>3.251388172</v>
+        <v>3.244530114</v>
       </c>
       <c r="Q68">
-        <v>4.137388172</v>
+        <v>4.130530114</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.208067652069533</v>
+        <v>0.212435572672893</v>
       </c>
       <c r="T68">
-        <v>1.943924659400248</v>
+        <v>1.996251222722526</v>
       </c>
       <c r="U68">
         <v>0.0535</v>
@@ -6883,7 +6883,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>8.183295497284384</v>
+        <v>8.061156758518944</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09627058898205468</v>
+        <v>0.09602187626046813</v>
       </c>
       <c r="C69">
-        <v>11.5827843463147</v>
+        <v>11.52259216860557</v>
       </c>
       <c r="D69">
-        <v>23.3039843463147</v>
+        <v>23.41939216860557</v>
       </c>
       <c r="E69">
-        <v>0.4652000000000012</v>
+        <v>0.6408000000000023</v>
       </c>
       <c r="F69">
-        <v>11.7652</v>
+        <v>11.9408</v>
       </c>
       <c r="G69">
         <v>0.044</v>
@@ -6927,28 +6927,28 @@
         <v>5.074</v>
       </c>
       <c r="M69">
-        <v>0.6294382000000001</v>
+        <v>0.6388328000000002</v>
       </c>
       <c r="N69">
-        <v>4.4445618</v>
+        <v>4.4351672</v>
       </c>
       <c r="O69">
-        <v>1.200031686</v>
+        <v>1.197495144</v>
       </c>
       <c r="P69">
-        <v>3.244530114</v>
+        <v>3.237672056</v>
       </c>
       <c r="Q69">
-        <v>4.130530114</v>
+        <v>4.123672055999999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.212435572672893</v>
+        <v>0.2170764883139629</v>
       </c>
       <c r="T69">
-        <v>1.996251222722526</v>
+        <v>2.051848196252447</v>
       </c>
       <c r="U69">
         <v>0.0535</v>
@@ -6965,7 +6965,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>8.061156758518944</v>
+        <v>7.942610335599547</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6973,22 +6973,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09602187626046813</v>
+        <v>0.09577316353888154</v>
       </c>
       <c r="C70">
-        <v>11.52259216860557</v>
+        <v>11.46354874320837</v>
       </c>
       <c r="D70">
-        <v>23.41939216860557</v>
+        <v>23.53594874320837</v>
       </c>
       <c r="E70">
-        <v>0.6408000000000023</v>
+        <v>0.8164000000000016</v>
       </c>
       <c r="F70">
-        <v>11.9408</v>
+        <v>12.1164</v>
       </c>
       <c r="G70">
         <v>0.044</v>
@@ -7009,28 +7009,28 @@
         <v>5.074</v>
       </c>
       <c r="M70">
-        <v>0.6388328000000002</v>
+        <v>0.6482274000000001</v>
       </c>
       <c r="N70">
-        <v>4.4351672</v>
+        <v>4.4257726</v>
       </c>
       <c r="O70">
-        <v>1.197495144</v>
+        <v>1.194958602</v>
       </c>
       <c r="P70">
-        <v>3.237672056</v>
+        <v>3.230813998</v>
       </c>
       <c r="Q70">
-        <v>4.123672055999999</v>
+        <v>4.116813998</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2170764883139629</v>
+        <v>0.2220168178673599</v>
       </c>
       <c r="T70">
-        <v>2.051848196252447</v>
+        <v>2.111032071300426</v>
       </c>
       <c r="U70">
         <v>0.0535</v>
@@ -7047,7 +7047,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>7.942610335599547</v>
+        <v>7.827500040880714</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7055,22 +7055,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09577316353888154</v>
+        <v>0.09552445081729501</v>
       </c>
       <c r="C71">
-        <v>11.46354874320837</v>
+        <v>11.40567130767777</v>
       </c>
       <c r="D71">
-        <v>23.53594874320837</v>
+        <v>23.65367130767777</v>
       </c>
       <c r="E71">
-        <v>0.8164000000000016</v>
+        <v>0.9920000000000027</v>
       </c>
       <c r="F71">
-        <v>12.1164</v>
+        <v>12.292</v>
       </c>
       <c r="G71">
         <v>0.044</v>
@@ -7091,28 +7091,28 @@
         <v>5.074</v>
       </c>
       <c r="M71">
-        <v>0.6482274000000001</v>
+        <v>0.6576220000000002</v>
       </c>
       <c r="N71">
-        <v>4.4257726</v>
+        <v>4.416378</v>
       </c>
       <c r="O71">
-        <v>1.194958602</v>
+        <v>1.19242206</v>
       </c>
       <c r="P71">
-        <v>3.230813998</v>
+        <v>3.22395594</v>
       </c>
       <c r="Q71">
-        <v>4.116813998</v>
+        <v>4.10995594</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2220168178673599</v>
+        <v>0.2272865027243167</v>
       </c>
       <c r="T71">
-        <v>2.111032071300426</v>
+        <v>2.174161538018272</v>
       </c>
       <c r="U71">
         <v>0.0535</v>
@@ -7129,7 +7129,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>7.827500040880714</v>
+        <v>7.715678611725275</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7137,22 +7137,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09552445081729501</v>
+        <v>0.09569037809570845</v>
       </c>
       <c r="C72">
-        <v>11.40567130767777</v>
+        <v>11.15140304629398</v>
       </c>
       <c r="D72">
-        <v>23.65367130767777</v>
+        <v>23.57500304629398</v>
       </c>
       <c r="E72">
-        <v>0.9920000000000027</v>
+        <v>1.167600000000002</v>
       </c>
       <c r="F72">
-        <v>12.292</v>
+        <v>12.4676</v>
       </c>
       <c r="G72">
         <v>0.044</v>
@@ -7173,45 +7173,45 @@
         <v>5.074</v>
       </c>
       <c r="M72">
-        <v>0.6576220000000002</v>
+        <v>0.6769906800000002</v>
       </c>
       <c r="N72">
-        <v>4.416378</v>
+        <v>4.39700932</v>
       </c>
       <c r="O72">
-        <v>1.19242206</v>
+        <v>1.1871925164</v>
       </c>
       <c r="P72">
-        <v>3.22395594</v>
+        <v>3.2098168036</v>
       </c>
       <c r="Q72">
-        <v>4.10995594</v>
+        <v>4.0958168036</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2272865027243167</v>
+        <v>0.2329196141231326</v>
       </c>
       <c r="T72">
-        <v>2.174161538018272</v>
+        <v>2.241644761061485</v>
       </c>
       <c r="U72">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V72">
         <v>0.27</v>
       </c>
       <c r="W72">
-        <v>0.039055</v>
+        <v>0.039639</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y72">
-        <v>7.715678611725275</v>
+        <v>7.494933312819016</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7219,22 +7219,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09569037809570845</v>
+        <v>0.0954475053741219</v>
       </c>
       <c r="C73">
-        <v>11.15140304629398</v>
+        <v>11.09113059615007</v>
       </c>
       <c r="D73">
-        <v>23.57500304629398</v>
+        <v>23.69033059615008</v>
       </c>
       <c r="E73">
-        <v>1.1676</v>
+        <v>1.343200000000001</v>
       </c>
       <c r="F73">
-        <v>12.4676</v>
+        <v>12.6432</v>
       </c>
       <c r="G73">
         <v>0.044</v>
@@ -7255,28 +7255,28 @@
         <v>5.074</v>
       </c>
       <c r="M73">
-        <v>0.6769906800000001</v>
+        <v>0.6865257600000001</v>
       </c>
       <c r="N73">
-        <v>4.39700932</v>
+        <v>4.38747424</v>
       </c>
       <c r="O73">
-        <v>1.1871925164</v>
+        <v>1.1846180448</v>
       </c>
       <c r="P73">
-        <v>3.2098168036</v>
+        <v>3.2028561952</v>
       </c>
       <c r="Q73">
-        <v>4.0958168036</v>
+        <v>4.0888561952</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2329196141231326</v>
+        <v>0.2389550906218639</v>
       </c>
       <c r="T73">
-        <v>2.241644761061484</v>
+        <v>2.31394821432207</v>
       </c>
       <c r="U73">
         <v>0.0543</v>
@@ -7293,7 +7293,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>7.494933312819017</v>
+        <v>7.390837016807642</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7301,22 +7301,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.0954475053741219</v>
+        <v>0.09520463265253531</v>
       </c>
       <c r="C74">
-        <v>11.09113059615007</v>
+        <v>11.03199204436363</v>
       </c>
       <c r="D74">
-        <v>23.69033059615008</v>
+        <v>23.80679204436363</v>
       </c>
       <c r="E74">
-        <v>1.343200000000001</v>
+        <v>1.518800000000001</v>
       </c>
       <c r="F74">
-        <v>12.6432</v>
+        <v>12.8188</v>
       </c>
       <c r="G74">
         <v>0.044</v>
@@ -7337,28 +7337,28 @@
         <v>5.074</v>
       </c>
       <c r="M74">
-        <v>0.6865257600000001</v>
+        <v>0.6960608400000001</v>
       </c>
       <c r="N74">
-        <v>4.38747424</v>
+        <v>4.377939159999999</v>
       </c>
       <c r="O74">
-        <v>1.1846180448</v>
+        <v>1.1820435732</v>
       </c>
       <c r="P74">
-        <v>3.2028561952</v>
+        <v>3.1958955868</v>
       </c>
       <c r="Q74">
-        <v>4.0888561952</v>
+        <v>4.0818955868</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2389550906218639</v>
+        <v>0.2454376394538345</v>
       </c>
       <c r="T74">
-        <v>2.31394821432207</v>
+        <v>2.391607478935291</v>
       </c>
       <c r="U74">
         <v>0.0543</v>
@@ -7375,7 +7375,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>7.390837016807642</v>
+        <v>7.289592674111646</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7383,22 +7383,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09520463265253531</v>
+        <v>0.09496175993094878</v>
       </c>
       <c r="C75">
-        <v>11.03199204436363</v>
+        <v>10.9740041962512</v>
       </c>
       <c r="D75">
-        <v>23.80679204436363</v>
+        <v>23.9244041962512</v>
       </c>
       <c r="E75">
-        <v>1.518800000000001</v>
+        <v>1.694400000000002</v>
       </c>
       <c r="F75">
-        <v>12.8188</v>
+        <v>12.9944</v>
       </c>
       <c r="G75">
         <v>0.044</v>
@@ -7419,28 +7419,28 @@
         <v>5.074</v>
       </c>
       <c r="M75">
-        <v>0.6960608400000001</v>
+        <v>0.7055959200000002</v>
       </c>
       <c r="N75">
-        <v>4.377939159999999</v>
+        <v>4.368404079999999</v>
       </c>
       <c r="O75">
-        <v>1.1820435732</v>
+        <v>1.1794691016</v>
       </c>
       <c r="P75">
-        <v>3.1958955868</v>
+        <v>3.1889349784</v>
       </c>
       <c r="Q75">
-        <v>4.0818955868</v>
+        <v>4.0749349784</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2454376394538345</v>
+        <v>0.2524188458882645</v>
       </c>
       <c r="T75">
-        <v>2.391607478935291</v>
+        <v>2.475240533134146</v>
       </c>
       <c r="U75">
         <v>0.0543</v>
@@ -7457,7 +7457,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>7.289592674111646</v>
+        <v>7.191084665002029</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7465,22 +7465,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09496175993094878</v>
+        <v>0.09471888720936222</v>
       </c>
       <c r="C76">
-        <v>10.9740041962512</v>
+        <v>10.91718419086989</v>
       </c>
       <c r="D76">
-        <v>23.9244041962512</v>
+        <v>24.04318419086989</v>
       </c>
       <c r="E76">
-        <v>1.694400000000002</v>
+        <v>1.870000000000001</v>
       </c>
       <c r="F76">
-        <v>12.9944</v>
+        <v>13.17</v>
       </c>
       <c r="G76">
         <v>0.044</v>
@@ -7501,28 +7501,28 @@
         <v>5.074</v>
       </c>
       <c r="M76">
-        <v>0.7055959200000002</v>
+        <v>0.7151310000000001</v>
       </c>
       <c r="N76">
-        <v>4.368404079999999</v>
+        <v>4.358868999999999</v>
       </c>
       <c r="O76">
-        <v>1.1794691016</v>
+        <v>1.17689463</v>
       </c>
       <c r="P76">
-        <v>3.1889349784</v>
+        <v>3.18197437</v>
       </c>
       <c r="Q76">
-        <v>4.0749349784</v>
+        <v>4.06797437</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2524188458882645</v>
+        <v>0.2599585488374489</v>
       </c>
       <c r="T76">
-        <v>2.475240533134146</v>
+        <v>2.565564231668909</v>
       </c>
       <c r="U76">
         <v>0.0543</v>
@@ -7539,7 +7539,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>7.191084665002029</v>
+        <v>7.095203536135336</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7547,22 +7547,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09471888720936222</v>
+        <v>0.09447601448777568</v>
       </c>
       <c r="C77">
-        <v>10.91718419086989</v>
+        <v>10.86154950934332</v>
       </c>
       <c r="D77">
-        <v>24.04318419086989</v>
+        <v>24.16314950934332</v>
       </c>
       <c r="E77">
-        <v>1.870000000000001</v>
+        <v>2.0456</v>
       </c>
       <c r="F77">
-        <v>13.17</v>
+        <v>13.3456</v>
       </c>
       <c r="G77">
         <v>0.044</v>
@@ -7583,28 +7583,28 @@
         <v>5.074</v>
       </c>
       <c r="M77">
-        <v>0.7151310000000001</v>
+        <v>0.7246660800000001</v>
       </c>
       <c r="N77">
-        <v>4.358868999999999</v>
+        <v>4.349333919999999</v>
       </c>
       <c r="O77">
-        <v>1.17689463</v>
+        <v>1.1743201584</v>
       </c>
       <c r="P77">
-        <v>3.18197437</v>
+        <v>3.1750137616</v>
       </c>
       <c r="Q77">
-        <v>4.06797437</v>
+        <v>4.0610137616</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2599585488374489</v>
+        <v>0.268126560365732</v>
       </c>
       <c r="T77">
-        <v>2.565564231668909</v>
+        <v>2.663414905081569</v>
       </c>
       <c r="U77">
         <v>0.0543</v>
@@ -7621,7 +7621,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>7.095203536135336</v>
+        <v>7.001845594870397</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7629,22 +7629,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.09447601448777568</v>
+        <v>0.09423314176618912</v>
       </c>
       <c r="C78">
-        <v>10.86154950934332</v>
+        <v>10.80711798343834</v>
       </c>
       <c r="D78">
-        <v>24.16314950934332</v>
+        <v>24.28431798343835</v>
       </c>
       <c r="E78">
-        <v>2.0456</v>
+        <v>2.221200000000001</v>
       </c>
       <c r="F78">
-        <v>13.3456</v>
+        <v>13.5212</v>
       </c>
       <c r="G78">
         <v>0.044</v>
@@ -7665,28 +7665,28 @@
         <v>5.074</v>
       </c>
       <c r="M78">
-        <v>0.7246660800000001</v>
+        <v>0.7342011600000001</v>
       </c>
       <c r="N78">
-        <v>4.349333919999999</v>
+        <v>4.339798839999999</v>
       </c>
       <c r="O78">
-        <v>1.1743201584</v>
+        <v>1.1717456868</v>
       </c>
       <c r="P78">
-        <v>3.1750137616</v>
+        <v>3.168053153199999</v>
       </c>
       <c r="Q78">
-        <v>4.0610137616</v>
+        <v>4.054053153199999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.268126560365732</v>
+        <v>0.2770048337660396</v>
       </c>
       <c r="T78">
-        <v>2.663414905081569</v>
+        <v>2.769774332704024</v>
       </c>
       <c r="U78">
         <v>0.0543</v>
@@ -7703,7 +7703,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>7.001845594870397</v>
+        <v>6.910912535196755</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7711,22 +7711,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.09423314176618912</v>
+        <v>0.09399026904460255</v>
       </c>
       <c r="C79">
-        <v>10.80711798343834</v>
+        <v>10.75390780440101</v>
       </c>
       <c r="D79">
-        <v>24.28431798343835</v>
+        <v>24.40670780440101</v>
       </c>
       <c r="E79">
-        <v>2.221200000000001</v>
+        <v>2.396800000000001</v>
       </c>
       <c r="F79">
-        <v>13.5212</v>
+        <v>13.6968</v>
       </c>
       <c r="G79">
         <v>0.044</v>
@@ -7747,28 +7747,28 @@
         <v>5.074</v>
       </c>
       <c r="M79">
-        <v>0.7342011600000001</v>
+        <v>0.74373624</v>
       </c>
       <c r="N79">
-        <v>4.339798839999999</v>
+        <v>4.330263759999999</v>
       </c>
       <c r="O79">
-        <v>1.1717456868</v>
+        <v>1.1691712152</v>
       </c>
       <c r="P79">
-        <v>3.168053153199999</v>
+        <v>3.161092544799999</v>
       </c>
       <c r="Q79">
-        <v>4.054053153199999</v>
+        <v>4.047092544799999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2770048337660396</v>
+        <v>0.2866902229300116</v>
       </c>
       <c r="T79">
-        <v>2.769774332704024</v>
+        <v>2.885802799201249</v>
       </c>
       <c r="U79">
         <v>0.0543</v>
@@ -7785,7 +7785,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>6.910912535196755</v>
+        <v>6.822311092437824</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7793,22 +7793,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09399026904460255</v>
+        <v>0.093747396323016</v>
       </c>
       <c r="C80">
-        <v>10.75390780440101</v>
+        <v>10.70193753206105</v>
       </c>
       <c r="D80">
-        <v>24.40670780440101</v>
+        <v>24.53033753206105</v>
       </c>
       <c r="E80">
-        <v>2.396800000000001</v>
+        <v>2.572400000000002</v>
       </c>
       <c r="F80">
-        <v>13.6968</v>
+        <v>13.8724</v>
       </c>
       <c r="G80">
         <v>0.044</v>
@@ -7829,28 +7829,28 @@
         <v>5.074</v>
       </c>
       <c r="M80">
-        <v>0.74373624</v>
+        <v>0.7532713200000002</v>
       </c>
       <c r="N80">
-        <v>4.330263759999999</v>
+        <v>4.320728679999999</v>
       </c>
       <c r="O80">
-        <v>1.1691712152</v>
+        <v>1.1665967436</v>
       </c>
       <c r="P80">
-        <v>3.161092544799999</v>
+        <v>3.154131936399999</v>
       </c>
       <c r="Q80">
-        <v>4.047092544799999</v>
+        <v>4.040131936399999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2866902229300116</v>
+        <v>0.2972980301096</v>
       </c>
       <c r="T80">
-        <v>2.885802799201249</v>
+        <v>3.012881595841067</v>
       </c>
       <c r="U80">
         <v>0.0543</v>
@@ -7867,7 +7867,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>6.822311092437824</v>
+        <v>6.735952724179115</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7875,22 +7875,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.093747396323016</v>
+        <v>0.09350452360142944</v>
       </c>
       <c r="C81">
-        <v>10.70193753206105</v>
+        <v>10.65122610421462</v>
       </c>
       <c r="D81">
-        <v>24.53033753206105</v>
+        <v>24.65522610421462</v>
       </c>
       <c r="E81">
-        <v>2.572400000000002</v>
+        <v>2.748000000000001</v>
       </c>
       <c r="F81">
-        <v>13.8724</v>
+        <v>14.048</v>
       </c>
       <c r="G81">
         <v>0.044</v>
@@ -7911,28 +7911,28 @@
         <v>5.074</v>
       </c>
       <c r="M81">
-        <v>0.7532713200000002</v>
+        <v>0.7628064000000001</v>
       </c>
       <c r="N81">
-        <v>4.320728679999999</v>
+        <v>4.311193599999999</v>
       </c>
       <c r="O81">
-        <v>1.1665967436</v>
+        <v>1.164022272</v>
       </c>
       <c r="P81">
-        <v>3.154131936399999</v>
+        <v>3.147171327999999</v>
       </c>
       <c r="Q81">
-        <v>4.040131936399999</v>
+        <v>4.033171327999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2972980301096</v>
+        <v>0.3089666180071473</v>
       </c>
       <c r="T81">
-        <v>3.012881595841067</v>
+        <v>3.152668272144866</v>
       </c>
       <c r="U81">
         <v>0.0543</v>
@@ -7949,7 +7949,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>6.735952724179115</v>
+        <v>6.651753315126877</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7957,22 +7957,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09350452360142944</v>
+        <v>0.09326165087984288</v>
       </c>
       <c r="C82">
-        <v>10.65122610421462</v>
+        <v>10.60179284629492</v>
       </c>
       <c r="D82">
-        <v>24.65522610421462</v>
+        <v>24.78139284629492</v>
       </c>
       <c r="E82">
-        <v>2.748000000000001</v>
+        <v>2.923600000000002</v>
       </c>
       <c r="F82">
-        <v>14.048</v>
+        <v>14.2236</v>
       </c>
       <c r="G82">
         <v>0.044</v>
@@ -7993,28 +7993,28 @@
         <v>5.074</v>
       </c>
       <c r="M82">
-        <v>0.7628064000000001</v>
+        <v>0.7723414800000001</v>
       </c>
       <c r="N82">
-        <v>4.311193599999999</v>
+        <v>4.30165852</v>
       </c>
       <c r="O82">
-        <v>1.164022272</v>
+        <v>1.1614478004</v>
       </c>
       <c r="P82">
-        <v>3.147171327999999</v>
+        <v>3.1402107196</v>
       </c>
       <c r="Q82">
-        <v>4.033171327999999</v>
+        <v>4.0262107196</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3089666180071473</v>
+        <v>0.3218634783149626</v>
       </c>
       <c r="T82">
-        <v>3.152668272144866</v>
+        <v>3.307169335428013</v>
       </c>
       <c r="U82">
         <v>0.0543</v>
@@ -8031,7 +8031,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>6.651753315126877</v>
+        <v>6.569632903829016</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8039,22 +8039,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09326165087984288</v>
+        <v>0.09301877815825633</v>
       </c>
       <c r="C83">
-        <v>10.60179284629492</v>
+        <v>10.55365748134144</v>
       </c>
       <c r="D83">
-        <v>24.78139284629492</v>
+        <v>24.90885748134144</v>
       </c>
       <c r="E83">
-        <v>2.923600000000002</v>
+        <v>3.099200000000002</v>
       </c>
       <c r="F83">
-        <v>14.2236</v>
+        <v>14.3992</v>
       </c>
       <c r="G83">
         <v>0.044</v>
@@ -8075,28 +8075,28 @@
         <v>5.074</v>
       </c>
       <c r="M83">
-        <v>0.7723414800000001</v>
+        <v>0.7818765600000002</v>
       </c>
       <c r="N83">
-        <v>4.30165852</v>
+        <v>4.292123439999999</v>
       </c>
       <c r="O83">
-        <v>1.1614478004</v>
+        <v>1.1588733288</v>
       </c>
       <c r="P83">
-        <v>3.1402107196</v>
+        <v>3.133250111199999</v>
       </c>
       <c r="Q83">
-        <v>4.0262107196</v>
+        <v>4.019250111199999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3218634783149626</v>
+        <v>0.3361933231014242</v>
       </c>
       <c r="T83">
-        <v>3.307169335428013</v>
+        <v>3.478837183520399</v>
       </c>
       <c r="U83">
         <v>0.0543</v>
@@ -8113,7 +8113,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>6.569632903829016</v>
+        <v>6.489515429392075</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8121,22 +8121,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09301877815825633</v>
+        <v>0.09277590543666979</v>
       </c>
       <c r="C84">
-        <v>10.55365748134144</v>
+        <v>10.50684014027838</v>
       </c>
       <c r="D84">
-        <v>24.90885748134144</v>
+        <v>25.03764014027839</v>
       </c>
       <c r="E84">
-        <v>3.099200000000002</v>
+        <v>3.274800000000003</v>
       </c>
       <c r="F84">
-        <v>14.3992</v>
+        <v>14.5748</v>
       </c>
       <c r="G84">
         <v>0.044</v>
@@ -8157,28 +8157,28 @@
         <v>5.074</v>
       </c>
       <c r="M84">
-        <v>0.7818765600000002</v>
+        <v>0.7914116400000002</v>
       </c>
       <c r="N84">
-        <v>4.292123439999999</v>
+        <v>4.28258836</v>
       </c>
       <c r="O84">
-        <v>1.1588733288</v>
+        <v>1.1562988572</v>
       </c>
       <c r="P84">
-        <v>3.133250111199999</v>
+        <v>3.1262895028</v>
       </c>
       <c r="Q84">
-        <v>4.019250111199999</v>
+        <v>4.0122895028</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3361933231014242</v>
+        <v>0.3522090319804106</v>
       </c>
       <c r="T84">
-        <v>3.478837183520399</v>
+        <v>3.670701249035418</v>
       </c>
       <c r="U84">
         <v>0.0543</v>
@@ -8195,7 +8195,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>6.489515429392075</v>
+        <v>6.411328496507834</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8203,22 +8203,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09277590543666979</v>
+        <v>0.09253303271508323</v>
       </c>
       <c r="C85">
-        <v>10.50684014027838</v>
+        <v>10.46136137251358</v>
       </c>
       <c r="D85">
-        <v>25.03764014027839</v>
+        <v>25.16776137251358</v>
       </c>
       <c r="E85">
-        <v>3.274800000000003</v>
+        <v>3.450400000000002</v>
       </c>
       <c r="F85">
-        <v>14.5748</v>
+        <v>14.7504</v>
       </c>
       <c r="G85">
         <v>0.044</v>
@@ -8239,28 +8239,28 @@
         <v>5.074</v>
       </c>
       <c r="M85">
-        <v>0.7914116400000002</v>
+        <v>0.8009467200000001</v>
       </c>
       <c r="N85">
-        <v>4.28258836</v>
+        <v>4.27305328</v>
       </c>
       <c r="O85">
-        <v>1.1562988572</v>
+        <v>1.1537243856</v>
       </c>
       <c r="P85">
-        <v>3.1262895028</v>
+        <v>3.1193288944</v>
       </c>
       <c r="Q85">
-        <v>4.0122895028</v>
+        <v>4.0053288944</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3522090319804106</v>
+        <v>0.3702267044692704</v>
       </c>
       <c r="T85">
-        <v>3.670701249035418</v>
+        <v>3.886548322739815</v>
       </c>
       <c r="U85">
         <v>0.0543</v>
@@ -8277,7 +8277,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>6.411328496507834</v>
+        <v>6.335003157263693</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8285,22 +8285,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09253303271508323</v>
+        <v>0.09229015999349666</v>
       </c>
       <c r="C86">
-        <v>10.46136137251358</v>
+        <v>10.41724215686964</v>
       </c>
       <c r="D86">
-        <v>25.16776137251358</v>
+        <v>25.29924215686965</v>
       </c>
       <c r="E86">
-        <v>3.4504</v>
+        <v>3.626000000000001</v>
       </c>
       <c r="F86">
-        <v>14.7504</v>
+        <v>14.926</v>
       </c>
       <c r="G86">
         <v>0.044</v>
@@ -8321,28 +8321,28 @@
         <v>5.074</v>
       </c>
       <c r="M86">
-        <v>0.8009467200000001</v>
+        <v>0.8104818000000001</v>
       </c>
       <c r="N86">
-        <v>4.27305328</v>
+        <v>4.2635182</v>
       </c>
       <c r="O86">
-        <v>1.1537243856</v>
+        <v>1.151149914</v>
       </c>
       <c r="P86">
-        <v>3.1193288944</v>
+        <v>3.112368286</v>
       </c>
       <c r="Q86">
-        <v>4.0053288944</v>
+        <v>3.998368286</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3702267044692701</v>
+        <v>0.3906467332899777</v>
       </c>
       <c r="T86">
-        <v>3.886548322739812</v>
+        <v>4.131175006271461</v>
       </c>
       <c r="U86">
         <v>0.0543</v>
@@ -8359,7 +8359,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>6.335003157263693</v>
+        <v>6.260473708354708</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8367,22 +8367,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.09229015999349666</v>
+        <v>0.09204728727191011</v>
       </c>
       <c r="C87">
-        <v>10.41724215686964</v>
+        <v>10.37450391285956</v>
       </c>
       <c r="D87">
-        <v>25.29924215686965</v>
+        <v>25.43210391285956</v>
       </c>
       <c r="E87">
-        <v>3.626000000000001</v>
+        <v>3.801600000000001</v>
       </c>
       <c r="F87">
-        <v>14.926</v>
+        <v>15.1016</v>
       </c>
       <c r="G87">
         <v>0.044</v>
@@ -8403,28 +8403,28 @@
         <v>5.074</v>
       </c>
       <c r="M87">
-        <v>0.8104818000000001</v>
+        <v>0.8200168800000001</v>
       </c>
       <c r="N87">
-        <v>4.2635182</v>
+        <v>4.25398312</v>
       </c>
       <c r="O87">
-        <v>1.151149914</v>
+        <v>1.1485754424</v>
       </c>
       <c r="P87">
-        <v>3.112368286</v>
+        <v>3.1054076776</v>
       </c>
       <c r="Q87">
-        <v>3.998368286</v>
+        <v>3.9914076776</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3906467332899777</v>
+        <v>0.4139839090850722</v>
       </c>
       <c r="T87">
-        <v>4.131175006271461</v>
+        <v>4.41074835887906</v>
       </c>
       <c r="U87">
         <v>0.0543</v>
@@ -8441,7 +8441,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>6.260473708354708</v>
+        <v>6.187677502443607</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8449,22 +8449,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.09204728727191011</v>
+        <v>0.09180441455032354</v>
       </c>
       <c r="C88">
-        <v>10.37450391285956</v>
+        <v>10.33316851231951</v>
       </c>
       <c r="D88">
-        <v>25.43210391285956</v>
+        <v>25.56636851231951</v>
       </c>
       <c r="E88">
-        <v>3.801600000000001</v>
+        <v>3.977200000000002</v>
       </c>
       <c r="F88">
-        <v>15.1016</v>
+        <v>15.2772</v>
       </c>
       <c r="G88">
         <v>0.044</v>
@@ -8485,28 +8485,28 @@
         <v>5.074</v>
       </c>
       <c r="M88">
-        <v>0.8200168800000001</v>
+        <v>0.8295519600000001</v>
       </c>
       <c r="N88">
-        <v>4.25398312</v>
+        <v>4.24444804</v>
       </c>
       <c r="O88">
-        <v>1.1485754424</v>
+        <v>1.1460009708</v>
       </c>
       <c r="P88">
-        <v>3.1054076776</v>
+        <v>3.0984470692</v>
       </c>
       <c r="Q88">
-        <v>3.9914076776</v>
+        <v>3.9844470692</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4139839090850722</v>
+        <v>0.4409114196178734</v>
       </c>
       <c r="T88">
-        <v>4.41074835887906</v>
+        <v>4.733332996503211</v>
       </c>
       <c r="U88">
         <v>0.0543</v>
@@ -8523,7 +8523,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>6.187677502443607</v>
+        <v>6.116554772530463</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8531,22 +8531,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.09180441455032354</v>
+        <v>0.09220394182873701</v>
       </c>
       <c r="C89">
-        <v>10.33316851231951</v>
+        <v>9.937447952985535</v>
       </c>
       <c r="D89">
-        <v>25.56636851231951</v>
+        <v>25.34624795298554</v>
       </c>
       <c r="E89">
-        <v>3.977200000000002</v>
+        <v>4.152800000000001</v>
       </c>
       <c r="F89">
-        <v>15.2772</v>
+        <v>15.4528</v>
       </c>
       <c r="G89">
         <v>0.044</v>
@@ -8567,45 +8567,45 @@
         <v>5.074</v>
       </c>
       <c r="M89">
-        <v>0.8295519600000001</v>
+        <v>0.8545398400000002</v>
       </c>
       <c r="N89">
-        <v>4.24444804</v>
+        <v>4.21946016</v>
       </c>
       <c r="O89">
-        <v>1.1460009708</v>
+        <v>1.1392542432</v>
       </c>
       <c r="P89">
-        <v>3.0984470692</v>
+        <v>3.0802059168</v>
       </c>
       <c r="Q89">
-        <v>3.9844470692</v>
+        <v>3.9662059168</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4409114196178734</v>
+        <v>0.4723268485728084</v>
       </c>
       <c r="T89">
-        <v>4.733332996503211</v>
+        <v>5.109681740398057</v>
       </c>
       <c r="U89">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V89">
         <v>0.27</v>
       </c>
       <c r="W89">
-        <v>0.039639</v>
+        <v>0.040369</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y89">
-        <v>6.116554772530463</v>
+        <v>5.937698586411137</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8613,22 +8613,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.09220394182873701</v>
+        <v>0.09196836910715045</v>
       </c>
       <c r="C90">
-        <v>9.937447952985535</v>
+        <v>9.891176424572542</v>
       </c>
       <c r="D90">
-        <v>25.34624795298554</v>
+        <v>25.47557642457254</v>
       </c>
       <c r="E90">
-        <v>4.152800000000001</v>
+        <v>4.328400000000002</v>
       </c>
       <c r="F90">
-        <v>15.4528</v>
+        <v>15.6284</v>
       </c>
       <c r="G90">
         <v>0.044</v>
@@ -8649,28 +8649,28 @@
         <v>5.074</v>
       </c>
       <c r="M90">
-        <v>0.8545398400000002</v>
+        <v>0.8642505200000001</v>
       </c>
       <c r="N90">
-        <v>4.21946016</v>
+        <v>4.209749479999999</v>
       </c>
       <c r="O90">
-        <v>1.1392542432</v>
+        <v>1.1366323596</v>
       </c>
       <c r="P90">
-        <v>3.0802059168</v>
+        <v>3.073117120399999</v>
       </c>
       <c r="Q90">
-        <v>3.9662059168</v>
+        <v>3.959117120399999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4723268485728084</v>
+        <v>0.5094541737013677</v>
       </c>
       <c r="T90">
-        <v>5.109681740398057</v>
+        <v>5.554457528637418</v>
       </c>
       <c r="U90">
         <v>0.0553</v>
@@ -8687,7 +8687,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>5.937698586411137</v>
+        <v>5.870982871957079</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8695,22 +8695,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.09196836910715045</v>
+        <v>0.09173279638556389</v>
       </c>
       <c r="C91">
-        <v>9.891176424572542</v>
+        <v>9.846231454193362</v>
       </c>
       <c r="D91">
-        <v>25.47557642457254</v>
+        <v>25.60623145419336</v>
       </c>
       <c r="E91">
-        <v>4.328400000000002</v>
+        <v>4.504000000000001</v>
       </c>
       <c r="F91">
-        <v>15.6284</v>
+        <v>15.804</v>
       </c>
       <c r="G91">
         <v>0.044</v>
@@ -8731,28 +8731,28 @@
         <v>5.074</v>
       </c>
       <c r="M91">
-        <v>0.8642505200000001</v>
+        <v>0.8739612000000001</v>
       </c>
       <c r="N91">
-        <v>4.209749479999999</v>
+        <v>4.2000388</v>
       </c>
       <c r="O91">
-        <v>1.1366323596</v>
+        <v>1.134010476</v>
       </c>
       <c r="P91">
-        <v>3.073117120399999</v>
+        <v>3.066028323999999</v>
       </c>
       <c r="Q91">
-        <v>3.959117120399999</v>
+        <v>3.952028324</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5094541737013677</v>
+        <v>0.554006963855639</v>
       </c>
       <c r="T91">
-        <v>5.554457528637418</v>
+        <v>6.088188474524653</v>
       </c>
       <c r="U91">
         <v>0.0553</v>
@@ -8769,7 +8769,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>5.870982871957079</v>
+        <v>5.805749728935334</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8777,22 +8777,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.09173279638556389</v>
+        <v>0.09149722366397733</v>
       </c>
       <c r="C92">
-        <v>9.846231454193362</v>
+        <v>9.802633557375716</v>
       </c>
       <c r="D92">
-        <v>25.60623145419336</v>
+        <v>25.73823355737572</v>
       </c>
       <c r="E92">
-        <v>4.504000000000001</v>
+        <v>4.679600000000002</v>
       </c>
       <c r="F92">
-        <v>15.804</v>
+        <v>15.9796</v>
       </c>
       <c r="G92">
         <v>0.044</v>
@@ -8813,28 +8813,28 @@
         <v>5.074</v>
       </c>
       <c r="M92">
-        <v>0.8739612000000001</v>
+        <v>0.8836718800000002</v>
       </c>
       <c r="N92">
-        <v>4.2000388</v>
+        <v>4.190328119999999</v>
       </c>
       <c r="O92">
-        <v>1.134010476</v>
+        <v>1.1313885924</v>
       </c>
       <c r="P92">
-        <v>3.066028323999999</v>
+        <v>3.0589395276</v>
       </c>
       <c r="Q92">
-        <v>3.952028324</v>
+        <v>3.9449395276</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.554006963855639</v>
+        <v>0.6084603740441927</v>
       </c>
       <c r="T92">
-        <v>6.088188474524653</v>
+        <v>6.740526297275718</v>
       </c>
       <c r="U92">
         <v>0.0553</v>
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>5.805749728935334</v>
+        <v>5.741950281364615</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8859,22 +8859,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.09149722366397733</v>
+        <v>0.09126165094239078</v>
       </c>
       <c r="C93">
-        <v>9.802633557375716</v>
+        <v>9.760403674875953</v>
       </c>
       <c r="D93">
-        <v>25.73823355737572</v>
+        <v>25.87160367487596</v>
       </c>
       <c r="E93">
-        <v>4.679600000000002</v>
+        <v>4.855200000000004</v>
       </c>
       <c r="F93">
-        <v>15.9796</v>
+        <v>16.1552</v>
       </c>
       <c r="G93">
         <v>0.044</v>
@@ -8895,28 +8895,28 @@
         <v>5.074</v>
       </c>
       <c r="M93">
-        <v>0.8836718800000002</v>
+        <v>0.8933825600000003</v>
       </c>
       <c r="N93">
-        <v>4.190328119999999</v>
+        <v>4.18061744</v>
       </c>
       <c r="O93">
-        <v>1.1313885924</v>
+        <v>1.1287667088</v>
       </c>
       <c r="P93">
-        <v>3.0589395276</v>
+        <v>3.0518507312</v>
       </c>
       <c r="Q93">
-        <v>3.9449395276</v>
+        <v>3.9378507312</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6084603740441927</v>
+        <v>0.6765271367798851</v>
       </c>
       <c r="T93">
-        <v>6.740526297275718</v>
+        <v>7.555948575714549</v>
       </c>
       <c r="U93">
         <v>0.0553</v>
@@ -8933,7 +8933,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>5.741950281364615</v>
+        <v>5.679537778306305</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8941,22 +8941,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.09126165094239078</v>
+        <v>0.09102607822080422</v>
       </c>
       <c r="C94">
-        <v>9.760403674875953</v>
+        <v>9.719563183753642</v>
       </c>
       <c r="D94">
-        <v>25.87160367487596</v>
+        <v>26.00636318375365</v>
       </c>
       <c r="E94">
-        <v>4.855200000000004</v>
+        <v>5.030800000000003</v>
       </c>
       <c r="F94">
-        <v>16.1552</v>
+        <v>16.3308</v>
       </c>
       <c r="G94">
         <v>0.044</v>
@@ -8977,28 +8977,28 @@
         <v>5.074</v>
       </c>
       <c r="M94">
-        <v>0.8933825600000003</v>
+        <v>0.9030932400000002</v>
       </c>
       <c r="N94">
-        <v>4.18061744</v>
+        <v>4.170906759999999</v>
       </c>
       <c r="O94">
-        <v>1.1287667088</v>
+        <v>1.1261448252</v>
       </c>
       <c r="P94">
-        <v>3.0518507312</v>
+        <v>3.044761934799999</v>
       </c>
       <c r="Q94">
-        <v>3.9378507312</v>
+        <v>3.9307619348</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6765271367798851</v>
+        <v>0.7640415460114893</v>
       </c>
       <c r="T94">
-        <v>7.555948575714549</v>
+        <v>8.604348647993046</v>
       </c>
       <c r="U94">
         <v>0.0553</v>
@@ -9015,7 +9015,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>5.679537778306305</v>
+        <v>5.618467479614838</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9023,22 +9023,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.09102607822080422</v>
+        <v>0.09079050549921767</v>
       </c>
       <c r="C95">
-        <v>9.719563183753642</v>
+        <v>9.680133908794094</v>
       </c>
       <c r="D95">
-        <v>26.00636318375365</v>
+        <v>26.1425339087941</v>
       </c>
       <c r="E95">
-        <v>5.030800000000003</v>
+        <v>5.206400000000002</v>
       </c>
       <c r="F95">
-        <v>16.3308</v>
+        <v>16.5064</v>
       </c>
       <c r="G95">
         <v>0.044</v>
@@ -9059,28 +9059,28 @@
         <v>5.074</v>
       </c>
       <c r="M95">
-        <v>0.9030932400000002</v>
+        <v>0.9128039200000002</v>
       </c>
       <c r="N95">
-        <v>4.170906759999999</v>
+        <v>4.16119608</v>
       </c>
       <c r="O95">
-        <v>1.1261448252</v>
+        <v>1.1235229416</v>
       </c>
       <c r="P95">
-        <v>3.044761934799999</v>
+        <v>3.0376731384</v>
       </c>
       <c r="Q95">
-        <v>3.9307619348</v>
+        <v>3.9236731384</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7640415460114893</v>
+        <v>0.880727424986962</v>
       </c>
       <c r="T95">
-        <v>8.604348647993046</v>
+        <v>10.00221541103104</v>
       </c>
       <c r="U95">
         <v>0.0553</v>
@@ -9097,7 +9097,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>5.618467479614838</v>
+        <v>5.558696548980638</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9105,22 +9105,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.09079050549921767</v>
+        <v>0.09055493277763113</v>
       </c>
       <c r="C96">
-        <v>9.680133908794094</v>
+        <v>9.642138134291692</v>
       </c>
       <c r="D96">
-        <v>26.1425339087941</v>
+        <v>26.28013813429169</v>
       </c>
       <c r="E96">
-        <v>5.206400000000002</v>
+        <v>5.382000000000001</v>
       </c>
       <c r="F96">
-        <v>16.5064</v>
+        <v>16.682</v>
       </c>
       <c r="G96">
         <v>0.044</v>
@@ -9141,28 +9141,28 @@
         <v>5.074</v>
       </c>
       <c r="M96">
-        <v>0.9128039200000002</v>
+        <v>0.9225146000000002</v>
       </c>
       <c r="N96">
-        <v>4.16119608</v>
+        <v>4.151485399999999</v>
       </c>
       <c r="O96">
-        <v>1.1235229416</v>
+        <v>1.120901058</v>
       </c>
       <c r="P96">
-        <v>3.0376731384</v>
+        <v>3.030584342</v>
       </c>
       <c r="Q96">
-        <v>3.9236731384</v>
+        <v>3.916584342</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.880727424986962</v>
+        <v>1.044087655552624</v>
       </c>
       <c r="T96">
-        <v>10.00221541103104</v>
+        <v>11.95922887928424</v>
       </c>
       <c r="U96">
         <v>0.0553</v>
@@ -9179,7 +9179,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>5.558696548980638</v>
+        <v>5.500183953728211</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9187,22 +9187,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.09055493277763113</v>
+        <v>0.09031936005604455</v>
       </c>
       <c r="C97">
-        <v>9.642138134291692</v>
+        <v>9.605598616207267</v>
       </c>
       <c r="D97">
-        <v>26.28013813429169</v>
+        <v>26.41919861620727</v>
       </c>
       <c r="E97">
-        <v>5.382000000000001</v>
+        <v>5.557600000000004</v>
       </c>
       <c r="F97">
-        <v>16.682</v>
+        <v>16.85760000000001</v>
       </c>
       <c r="G97">
         <v>0.044</v>
@@ -9223,28 +9223,28 @@
         <v>5.074</v>
       </c>
       <c r="M97">
-        <v>0.9225146000000002</v>
+        <v>0.9322252800000003</v>
       </c>
       <c r="N97">
-        <v>4.151485399999999</v>
+        <v>4.14177472</v>
       </c>
       <c r="O97">
-        <v>1.120901058</v>
+        <v>1.1182791744</v>
       </c>
       <c r="P97">
-        <v>3.030584342</v>
+        <v>3.0234955456</v>
       </c>
       <c r="Q97">
-        <v>3.916584342</v>
+        <v>3.9094955456</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.044087655552624</v>
+        <v>1.289128001401116</v>
       </c>
       <c r="T97">
-        <v>11.95922887928424</v>
+        <v>14.89474908166403</v>
       </c>
       <c r="U97">
         <v>0.0553</v>
@@ -9261,7 +9261,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>5.500183953728211</v>
+        <v>5.442890370876875</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9269,22 +9269,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.09031936005604457</v>
+        <v>0.09008378733445802</v>
       </c>
       <c r="C98">
-        <v>9.605598616207253</v>
+        <v>9.570538594713408</v>
       </c>
       <c r="D98">
-        <v>26.41919861620725</v>
+        <v>26.55973859471341</v>
       </c>
       <c r="E98">
-        <v>5.557600000000001</v>
+        <v>5.7332</v>
       </c>
       <c r="F98">
-        <v>16.8576</v>
+        <v>17.0332</v>
       </c>
       <c r="G98">
         <v>0.044</v>
@@ -9305,28 +9305,28 @@
         <v>5.074</v>
       </c>
       <c r="M98">
-        <v>0.9322252800000002</v>
+        <v>0.9419359600000001</v>
       </c>
       <c r="N98">
-        <v>4.14177472</v>
+        <v>4.132064039999999</v>
       </c>
       <c r="O98">
-        <v>1.1182791744</v>
+        <v>1.1156572908</v>
       </c>
       <c r="P98">
-        <v>3.0234955456</v>
+        <v>3.0164067492</v>
       </c>
       <c r="Q98">
-        <v>3.9094955456</v>
+        <v>3.9024067492</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.289128001401113</v>
+        <v>1.697528577815266</v>
       </c>
       <c r="T98">
-        <v>14.894749081664</v>
+        <v>19.78728275229697</v>
       </c>
       <c r="U98">
         <v>0.0553</v>
@@ -9343,7 +9343,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>5.442890370876875</v>
+        <v>5.386778099012165</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9351,22 +9351,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.09008378733445802</v>
+        <v>0.08984821461287144</v>
       </c>
       <c r="C99">
-        <v>9.570538594713408</v>
+        <v>9.536981807142638</v>
       </c>
       <c r="D99">
-        <v>26.55973859471341</v>
+        <v>26.70178180714264</v>
       </c>
       <c r="E99">
-        <v>5.7332</v>
+        <v>5.908800000000003</v>
       </c>
       <c r="F99">
-        <v>17.0332</v>
+        <v>17.2088</v>
       </c>
       <c r="G99">
         <v>0.044</v>
@@ -9387,28 +9387,28 @@
         <v>5.074</v>
       </c>
       <c r="M99">
-        <v>0.9419359600000001</v>
+        <v>0.9516466400000002</v>
       </c>
       <c r="N99">
-        <v>4.132064039999999</v>
+        <v>4.12235336</v>
       </c>
       <c r="O99">
-        <v>1.1156572908</v>
+        <v>1.1130354072</v>
       </c>
       <c r="P99">
-        <v>3.0164067492</v>
+        <v>3.0093179528</v>
       </c>
       <c r="Q99">
-        <v>3.9024067492</v>
+        <v>3.8953179528</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.697528577815266</v>
+        <v>2.51432973064357</v>
       </c>
       <c r="T99">
-        <v>19.78728275229697</v>
+        <v>29.57235009356291</v>
       </c>
       <c r="U99">
         <v>0.0553</v>
@@ -9425,7 +9425,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>5.386778099012165</v>
+        <v>5.331810975552858</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9433,22 +9433,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.08984821461287144</v>
+        <v>0.0896126418912849</v>
       </c>
       <c r="C100">
-        <v>9.536981807142638</v>
+        <v>9.504952501352928</v>
       </c>
       <c r="D100">
-        <v>26.70178180714264</v>
+        <v>26.84535250135293</v>
       </c>
       <c r="E100">
-        <v>5.908800000000003</v>
+        <v>6.084400000000002</v>
       </c>
       <c r="F100">
-        <v>17.2088</v>
+        <v>17.3844</v>
       </c>
       <c r="G100">
         <v>0.044</v>
@@ -9469,28 +9469,28 @@
         <v>5.074</v>
       </c>
       <c r="M100">
-        <v>0.9516466400000002</v>
+        <v>0.9613573200000002</v>
       </c>
       <c r="N100">
-        <v>4.12235336</v>
+        <v>4.11264268</v>
       </c>
       <c r="O100">
-        <v>1.1130354072</v>
+        <v>1.1104135236</v>
       </c>
       <c r="P100">
-        <v>3.0093179528</v>
+        <v>3.002229156399999</v>
       </c>
       <c r="Q100">
-        <v>3.8953179528</v>
+        <v>3.8882291564</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.51432973064357</v>
+        <v>4.964733189128485</v>
       </c>
       <c r="T100">
-        <v>29.57235009356291</v>
+        <v>58.92755211736075</v>
       </c>
       <c r="U100">
         <v>0.0553</v>
@@ -9507,91 +9507,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>5.331810975552858</v>
+        <v>5.277954299032121</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.0896126418912849</v>
-      </c>
-      <c r="C101">
-        <v>9.504952501352928</v>
-      </c>
-      <c r="D101">
-        <v>26.84535250135293</v>
-      </c>
-      <c r="E101">
-        <v>6.084400000000002</v>
-      </c>
-      <c r="F101">
-        <v>17.3844</v>
-      </c>
-      <c r="G101">
-        <v>0.044</v>
-      </c>
-      <c r="H101">
-        <v>6.26</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>5.96</v>
-      </c>
-      <c r="K101">
-        <v>0.886</v>
-      </c>
-      <c r="L101">
-        <v>5.074</v>
-      </c>
-      <c r="M101">
-        <v>0.9613573200000002</v>
-      </c>
-      <c r="N101">
-        <v>4.11264268</v>
-      </c>
-      <c r="O101">
-        <v>1.1104135236</v>
-      </c>
-      <c r="P101">
-        <v>3.002229156399999</v>
-      </c>
-      <c r="Q101">
-        <v>3.8882291564</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.964733189128485</v>
-      </c>
-      <c r="T101">
-        <v>58.92755211736075</v>
-      </c>
-      <c r="U101">
-        <v>0.0553</v>
-      </c>
-      <c r="V101">
-        <v>0.27</v>
-      </c>
-      <c r="W101">
-        <v>0.040369</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>A3/A-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>5.277954299032121</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
